--- a/output/OrderRepository.xlsx
+++ b/output/OrderRepository.xlsx
@@ -899,52 +899,68 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="92">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -956,292 +972,292 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true">
       <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1430,5351 +1446,5351 @@
   <dimension ref="A1:H223"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" customWidth="true" hidden="false" style="0" width="15.62" collapsed="false" outlineLevel="0"/>
-    <col min="3" max="3" customWidth="true" hidden="false" style="0" width="31.25" collapsed="false" outlineLevel="0"/>
-    <col min="4" max="4" customWidth="true" hidden="false" style="0" width="15.62" collapsed="false" outlineLevel="0"/>
-    <col min="5" max="5" customWidth="true" hidden="false" style="0" width="23.44" collapsed="false" outlineLevel="0"/>
-    <col min="6" max="6" customWidth="true" hidden="false" style="0" width="29.21" collapsed="false" outlineLevel="0"/>
-    <col min="7" max="7" customWidth="true" hidden="false" style="0" width="23.44" collapsed="false" outlineLevel="0"/>
-    <col min="8" max="8" customWidth="true" hidden="false" style="0" width="15.62" collapsed="false" outlineLevel="0"/>
+    <col min="1" max="2" customWidth="true" hidden="false" style="1" width="15.62" collapsed="false" outlineLevel="0"/>
+    <col min="3" max="3" customWidth="true" hidden="false" style="1" width="31.25" collapsed="false" outlineLevel="0"/>
+    <col min="4" max="4" customWidth="true" hidden="false" style="1" width="15.62" collapsed="false" outlineLevel="0"/>
+    <col min="5" max="5" customWidth="true" hidden="false" style="1" width="23.44" collapsed="false" outlineLevel="0"/>
+    <col min="6" max="6" customWidth="true" hidden="false" style="1" width="29.21" collapsed="false" outlineLevel="0"/>
+    <col min="7" max="7" customWidth="true" hidden="false" style="1" width="23.44" collapsed="false" outlineLevel="0"/>
+    <col min="8" max="8" customWidth="true" hidden="false" style="1" width="15.62" collapsed="false" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="2" t="s">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" ht="15.0" customHeight="true">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="23"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="B14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="A15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="D15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="B16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="5" t="n">
+      <c r="A17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>1.0</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="F17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="true">
-      <c r="A18" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="25" t="n">
+      <c r="A18" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="29" t="n">
         <v>2.0</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="28" t="s">
+      <c r="D18" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="30" t="s">
+      <c r="F18" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="true">
-      <c r="A19" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="25" t="n">
+      <c r="A19" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="29" t="n">
         <v>3.0</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="28" t="s">
+      <c r="D19" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="30" t="s">
+      <c r="F19" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="true">
-      <c r="A20" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="25" t="n">
+      <c r="A20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="29" t="n">
         <v>4.0</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="28" t="s">
+      <c r="D20" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="30" t="s">
+      <c r="F20" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="true">
-      <c r="A21" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="25" t="n">
+      <c r="A21" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="29" t="n">
         <v>5.0</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="28" t="s">
+      <c r="D21" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" s="30" t="s">
+      <c r="F21" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H21" s="31" t="s">
+      <c r="H21" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="true">
-      <c r="A22" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="25" t="n">
+      <c r="A22" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="29" t="n">
         <v>6.0</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="28" t="s">
+      <c r="D22" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="30" t="s">
+      <c r="F22" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="true">
-      <c r="A23" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="25" t="n">
+      <c r="A23" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="29" t="n">
         <v>7.0</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="28" t="s">
+      <c r="D23" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F23" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="30" t="s">
+      <c r="F23" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H23" s="31" t="s">
+      <c r="H23" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="true">
-      <c r="A24" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="25" t="n">
+      <c r="A24" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="29" t="n">
         <v>8.0</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="28" t="s">
+      <c r="D24" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="30" t="s">
+      <c r="F24" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="true">
-      <c r="A25" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="25" t="n">
+      <c r="A25" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="29" t="n">
         <v>9.0</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="28" t="s">
+      <c r="D25" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F25" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G25" s="30" t="s">
+      <c r="F25" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H25" s="31" t="s">
+      <c r="H25" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="true">
-      <c r="A26" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="25" t="n">
+      <c r="A26" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="29" t="n">
         <v>10.0</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="28" t="s">
+      <c r="D26" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G26" s="30" t="s">
+      <c r="F26" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H26" s="31" t="s">
+      <c r="H26" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="true">
-      <c r="A27" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="25" t="n">
+      <c r="A27" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="29" t="n">
         <v>11.0</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="28" t="s">
+      <c r="D27" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F27" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="30" t="s">
+      <c r="F27" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H27" s="31" t="s">
+      <c r="H27" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="true">
-      <c r="A28" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="25" t="n">
+      <c r="A28" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="29" t="n">
         <v>12.0</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="28" t="s">
+      <c r="D28" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="30" t="s">
+      <c r="F28" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" ht="15.0" customHeight="true">
-      <c r="A29" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="25" t="n">
+      <c r="A29" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="29" t="n">
         <v>13.0</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="28" t="s">
+      <c r="D29" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="F29" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G29" s="30" t="s">
+      <c r="F29" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" ht="15.0" customHeight="true">
-      <c r="A30" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="25" t="n">
+      <c r="A30" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="29" t="n">
         <v>14.0</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D30" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="28" t="s">
+      <c r="D30" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="F30" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" s="30" t="s">
+      <c r="F30" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H30" s="31" t="s">
+      <c r="H30" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="true">
-      <c r="A31" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="25" t="n">
+      <c r="A31" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="29" t="n">
         <v>15.0</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="28" t="s">
+      <c r="D31" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G31" s="30" t="s">
+      <c r="F31" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H31" s="31" t="s">
+      <c r="H31" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="32" ht="15.0" customHeight="true">
-      <c r="A32" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="25" t="n">
+      <c r="A32" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="29" t="n">
         <v>16.0</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="28" t="s">
+      <c r="D32" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="F32" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G32" s="30" t="s">
+      <c r="F32" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H32" s="31" t="s">
+      <c r="H32" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" ht="15.0" customHeight="true">
-      <c r="A33" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="25" t="n">
+      <c r="A33" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="29" t="n">
         <v>17.0</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="28" t="s">
+      <c r="D33" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="F33" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="30" t="s">
+      <c r="F33" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="H33" s="31" t="s">
+      <c r="H33" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="true">
-      <c r="A34" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="25" t="n">
+      <c r="A34" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="29" t="n">
         <v>18.0</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D34" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="28" t="s">
+      <c r="D34" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G34" s="30" t="s">
+      <c r="F34" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H34" s="31" t="s">
+      <c r="H34" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" ht="15.0" customHeight="true">
-      <c r="A35" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="25" t="n">
+      <c r="A35" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="29" t="n">
         <v>19.0</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D35" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" s="28" t="s">
+      <c r="D35" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="F35" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G35" s="30" t="s">
+      <c r="F35" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H35" s="31" t="s">
+      <c r="H35" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="true">
-      <c r="A36" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B36" s="25" t="n">
+      <c r="A36" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="29" t="n">
         <v>20.0</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="28" t="s">
+      <c r="D36" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" s="30" t="s">
+      <c r="F36" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H36" s="31" t="s">
+      <c r="H36" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" ht="15.0" customHeight="true">
-      <c r="A37" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B37" s="25" t="n">
+      <c r="A37" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="29" t="n">
         <v>21.0</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E37" s="28" t="s">
+      <c r="D37" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" s="30" t="s">
+      <c r="F37" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H37" s="31" t="s">
+      <c r="H37" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" ht="15.0" customHeight="true">
-      <c r="A38" s="32"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="39"/>
+      <c r="A38" s="36"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="43"/>
     </row>
     <row r="39" ht="15.0" customHeight="true">
-      <c r="A39" s="40" t="s">
+      <c r="A39" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="42" t="s">
+      <c r="B39" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="43"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="49"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="51"/>
     </row>
     <row r="40" ht="15.0" customHeight="true">
-      <c r="A40" s="48" t="s">
+      <c r="A40" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B40" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="50" t="s">
+      <c r="B40" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="51"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="53"/>
-      <c r="G40" s="54"/>
-      <c r="H40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="59"/>
     </row>
     <row r="41" ht="15.0" customHeight="true">
-      <c r="A41" s="56" t="s">
+      <c r="A41" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B41" s="57" t="s">
+      <c r="B41" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D41" s="59" t="s">
+      <c r="D41" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="60" t="s">
+      <c r="E41" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F41" s="61" t="s">
+      <c r="F41" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G41" s="62" t="s">
+      <c r="G41" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H41" s="63" t="s">
+      <c r="H41" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="true">
-      <c r="A42" s="64" t="s">
+      <c r="A42" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="G42" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" s="71" t="s">
+      <c r="B42" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="43" ht="15.0" customHeight="true">
-      <c r="A43" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B43" s="25" t="n">
+      <c r="A43" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="29" t="n">
         <v>1.0</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" s="28" t="s">
+      <c r="D43" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="F43" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" s="30" t="s">
+      <c r="F43" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="H43" s="31" t="s">
+      <c r="H43" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" ht="15.0" customHeight="true">
-      <c r="A44" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="25" t="n">
+      <c r="A44" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="29" t="n">
         <v>2.0</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E44" s="28" t="s">
+      <c r="D44" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="F44" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G44" s="30" t="s">
+      <c r="F44" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H44" s="31" t="s">
+      <c r="H44" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="true">
-      <c r="A45" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" s="25" t="n">
+      <c r="A45" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="29" t="n">
         <v>3.0</v>
       </c>
-      <c r="C45" s="26" t="s">
+      <c r="C45" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="28" t="s">
+      <c r="D45" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F45" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G45" s="30" t="s">
+      <c r="F45" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H45" s="31" t="s">
+      <c r="H45" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" ht="15.0" customHeight="true">
-      <c r="A46" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B46" s="25" t="n">
+      <c r="A46" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="29" t="n">
         <v>4.0</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="28" t="s">
+      <c r="D46" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F46" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G46" s="30" t="s">
+      <c r="F46" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H46" s="31" t="s">
+      <c r="H46" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="47" ht="15.0" customHeight="true">
-      <c r="A47" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47" s="25" t="n">
+      <c r="A47" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="29" t="n">
         <v>5.0</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E47" s="28" t="s">
+      <c r="D47" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G47" s="30" t="s">
+      <c r="F47" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H47" s="31" t="s">
+      <c r="H47" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="true">
-      <c r="A48" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B48" s="25" t="n">
+      <c r="A48" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="29" t="n">
         <v>6.0</v>
       </c>
-      <c r="C48" s="26" t="s">
+      <c r="C48" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D48" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="28" t="s">
+      <c r="D48" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F48" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G48" s="30" t="s">
+      <c r="F48" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H48" s="31" t="s">
+      <c r="H48" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" ht="15.0" customHeight="true">
-      <c r="A49" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" s="25" t="n">
+      <c r="A49" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="29" t="n">
         <v>7.0</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C49" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D49" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E49" s="28" t="s">
+      <c r="D49" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F49" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G49" s="30" t="s">
+      <c r="F49" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H49" s="31" t="s">
+      <c r="H49" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" ht="15.0" customHeight="true">
-      <c r="A50" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B50" s="25" t="n">
+      <c r="A50" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="29" t="n">
         <v>8.0</v>
       </c>
-      <c r="C50" s="26" t="s">
+      <c r="C50" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D50" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E50" s="28" t="s">
+      <c r="D50" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F50" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50" s="30" t="s">
+      <c r="F50" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H50" s="31" t="s">
+      <c r="H50" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="true">
-      <c r="A51" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B51" s="25" t="n">
+      <c r="A51" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="29" t="n">
         <v>9.0</v>
       </c>
-      <c r="C51" s="26" t="s">
+      <c r="C51" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D51" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E51" s="28" t="s">
+      <c r="D51" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F51" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G51" s="30" t="s">
+      <c r="F51" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H51" s="31" t="s">
+      <c r="H51" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" ht="15.0" customHeight="true">
-      <c r="A52" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="25" t="n">
+      <c r="A52" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="29" t="n">
         <v>10.0</v>
       </c>
-      <c r="C52" s="26" t="s">
+      <c r="C52" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D52" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E52" s="28" t="s">
+      <c r="D52" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="F52" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G52" s="30" t="s">
+      <c r="F52" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H52" s="31" t="s">
+      <c r="H52" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" ht="15.0" customHeight="true">
-      <c r="A53" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B53" s="25" t="n">
+      <c r="A53" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="29" t="n">
         <v>11.0</v>
       </c>
-      <c r="C53" s="26" t="s">
+      <c r="C53" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D53" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E53" s="28" t="s">
+      <c r="D53" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F53" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" s="30" t="s">
+      <c r="F53" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H53" s="31" t="s">
+      <c r="H53" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="true">
-      <c r="A54" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B54" s="25" t="n">
+      <c r="A54" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="29" t="n">
         <v>12.0</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D54" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E54" s="28" t="s">
+      <c r="D54" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="F54" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G54" s="30" t="s">
+      <c r="F54" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="H54" s="31" t="s">
+      <c r="H54" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55" ht="15.0" customHeight="true">
-      <c r="A55" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B55" s="25" t="n">
+      <c r="A55" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="29" t="n">
         <v>13.0</v>
       </c>
-      <c r="C55" s="26" t="s">
+      <c r="C55" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D55" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E55" s="28" t="s">
+      <c r="D55" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="F55" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G55" s="30" t="s">
+      <c r="F55" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H55" s="31" t="s">
+      <c r="H55" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="56" ht="15.0" customHeight="true">
-      <c r="A56" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B56" s="25" t="n">
+      <c r="A56" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="29" t="n">
         <v>14.0</v>
       </c>
-      <c r="C56" s="26" t="s">
+      <c r="C56" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D56" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E56" s="28" t="s">
+      <c r="D56" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="F56" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G56" s="30" t="s">
+      <c r="F56" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H56" s="31" t="s">
+      <c r="H56" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="true">
-      <c r="A57" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B57" s="25" t="n">
+      <c r="A57" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="29" t="n">
         <v>15.0</v>
       </c>
-      <c r="C57" s="26" t="s">
+      <c r="C57" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D57" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57" s="28" t="s">
+      <c r="D57" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="F57" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G57" s="30" t="s">
+      <c r="F57" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H57" s="31" t="s">
+      <c r="H57" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="58" ht="15.0" customHeight="true">
-      <c r="A58" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B58" s="25" t="n">
+      <c r="A58" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="29" t="n">
         <v>16.0</v>
       </c>
-      <c r="C58" s="26" t="s">
+      <c r="C58" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D58" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E58" s="28" t="s">
+      <c r="D58" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="F58" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58" s="30" t="s">
+      <c r="F58" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H58" s="31" t="s">
+      <c r="H58" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="59" ht="15.0" customHeight="true">
-      <c r="A59" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B59" s="25" t="n">
+      <c r="A59" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="29" t="n">
         <v>17.0</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="C59" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D59" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E59" s="28" t="s">
+      <c r="D59" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="F59" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G59" s="30" t="s">
+      <c r="F59" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="H59" s="31" t="s">
+      <c r="H59" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="60" ht="15.0" customHeight="true">
-      <c r="A60" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B60" s="25" t="n">
+      <c r="A60" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="29" t="n">
         <v>18.0</v>
       </c>
-      <c r="C60" s="26" t="s">
+      <c r="C60" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D60" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E60" s="28" t="s">
+      <c r="D60" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="F60" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G60" s="30" t="s">
+      <c r="F60" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="61" ht="15.0" customHeight="true">
-      <c r="A61" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B61" s="25" t="n">
+      <c r="A61" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="29" t="n">
         <v>19.0</v>
       </c>
-      <c r="C61" s="26" t="s">
+      <c r="C61" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D61" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E61" s="28" t="s">
+      <c r="D61" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="F61" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G61" s="30" t="s">
+      <c r="F61" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H61" s="31" t="s">
+      <c r="H61" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" ht="15.0" customHeight="true">
-      <c r="A62" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B62" s="25" t="n">
+      <c r="A62" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="29" t="n">
         <v>20.0</v>
       </c>
-      <c r="C62" s="26" t="s">
+      <c r="C62" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D62" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E62" s="28" t="s">
+      <c r="D62" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="F62" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G62" s="30" t="s">
+      <c r="F62" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H62" s="31" t="s">
+      <c r="H62" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="true">
-      <c r="A63" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B63" s="25" t="n">
+      <c r="A63" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="29" t="n">
         <v>21.0</v>
       </c>
-      <c r="C63" s="26" t="s">
+      <c r="C63" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D63" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E63" s="28" t="s">
+      <c r="D63" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="F63" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G63" s="30" t="s">
+      <c r="F63" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H63" s="31" t="s">
+      <c r="H63" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="64" ht="15.0" customHeight="true">
-      <c r="A64" s="72" t="s">
+      <c r="A64" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B64" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C64" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D64" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E64" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="F64" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="G64" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="H64" s="79" t="s">
+      <c r="B64" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D64" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="83" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="65" ht="15.0" customHeight="true">
-      <c r="A65" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B65" s="25" t="n">
+      <c r="A65" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="29" t="n">
         <v>1.0</v>
       </c>
-      <c r="C65" s="26" t="s">
+      <c r="C65" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="D65" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E65" s="28" t="s">
+      <c r="D65" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G65" s="30" t="s">
+      <c r="F65" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G65" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="H65" s="31" t="s">
+      <c r="H65" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="true">
-      <c r="A66" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B66" s="25" t="n">
+      <c r="A66" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="29" t="n">
         <v>2.0</v>
       </c>
-      <c r="C66" s="26" t="s">
+      <c r="C66" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D66" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E66" s="28" t="s">
+      <c r="D66" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="F66" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G66" s="30" t="s">
+      <c r="F66" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H66" s="31" t="s">
+      <c r="H66" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="67" ht="15.0" customHeight="true">
-      <c r="A67" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B67" s="25" t="n">
+      <c r="A67" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="29" t="n">
         <v>3.0</v>
       </c>
-      <c r="C67" s="26" t="s">
+      <c r="C67" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D67" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E67" s="28" t="s">
+      <c r="D67" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F67" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G67" s="30" t="s">
+      <c r="F67" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H67" s="31" t="s">
+      <c r="H67" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="68" ht="15.0" customHeight="true">
-      <c r="A68" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B68" s="25" t="n">
+      <c r="A68" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="29" t="n">
         <v>4.0</v>
       </c>
-      <c r="C68" s="26" t="s">
+      <c r="C68" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D68" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E68" s="28" t="s">
+      <c r="D68" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F68" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G68" s="30" t="s">
+      <c r="F68" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H68" s="31" t="s">
+      <c r="H68" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="true">
-      <c r="A69" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B69" s="25" t="n">
+      <c r="A69" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="29" t="n">
         <v>5.0</v>
       </c>
-      <c r="C69" s="26" t="s">
+      <c r="C69" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E69" s="28" t="s">
+      <c r="D69" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F69" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G69" s="30" t="s">
+      <c r="F69" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H69" s="31" t="s">
+      <c r="H69" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="70" ht="15.0" customHeight="true">
-      <c r="A70" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B70" s="25" t="n">
+      <c r="A70" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="29" t="n">
         <v>6.0</v>
       </c>
-      <c r="C70" s="26" t="s">
+      <c r="C70" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E70" s="28" t="s">
+      <c r="D70" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F70" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G70" s="30" t="s">
+      <c r="F70" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H70" s="31" t="s">
+      <c r="H70" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="71" ht="15.0" customHeight="true">
-      <c r="A71" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B71" s="25" t="n">
+      <c r="A71" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="29" t="n">
         <v>7.0</v>
       </c>
-      <c r="C71" s="26" t="s">
+      <c r="C71" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D71" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E71" s="28" t="s">
+      <c r="D71" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F71" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G71" s="30" t="s">
+      <c r="F71" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H71" s="31" t="s">
+      <c r="H71" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="true">
-      <c r="A72" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B72" s="25" t="n">
+      <c r="A72" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="29" t="n">
         <v>8.0</v>
       </c>
-      <c r="C72" s="26" t="s">
+      <c r="C72" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D72" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E72" s="28" t="s">
+      <c r="D72" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F72" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G72" s="30" t="s">
+      <c r="F72" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G72" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H72" s="31" t="s">
+      <c r="H72" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="73" ht="15.0" customHeight="true">
-      <c r="A73" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B73" s="25" t="n">
+      <c r="A73" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" s="29" t="n">
         <v>9.0</v>
       </c>
-      <c r="C73" s="26" t="s">
+      <c r="C73" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D73" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E73" s="28" t="s">
+      <c r="D73" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F73" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G73" s="30" t="s">
+      <c r="F73" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H73" s="31" t="s">
+      <c r="H73" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="74" ht="15.0" customHeight="true">
-      <c r="A74" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B74" s="25" t="n">
+      <c r="A74" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="29" t="n">
         <v>10.0</v>
       </c>
-      <c r="C74" s="26" t="s">
+      <c r="C74" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D74" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E74" s="28" t="s">
+      <c r="D74" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="F74" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G74" s="30" t="s">
+      <c r="F74" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H74" s="31" t="s">
+      <c r="H74" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="75" ht="15.0" customHeight="true">
-      <c r="A75" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B75" s="25" t="n">
+      <c r="A75" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" s="29" t="n">
         <v>11.0</v>
       </c>
-      <c r="C75" s="26" t="s">
+      <c r="C75" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D75" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E75" s="28" t="s">
+      <c r="D75" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F75" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G75" s="30" t="s">
+      <c r="F75" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H75" s="31" t="s">
+      <c r="H75" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="76" ht="15.0" customHeight="true">
-      <c r="A76" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B76" s="25" t="n">
+      <c r="A76" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="29" t="n">
         <v>12.0</v>
       </c>
-      <c r="C76" s="26" t="s">
+      <c r="C76" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D76" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E76" s="28" t="s">
+      <c r="D76" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="F76" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G76" s="30" t="s">
+      <c r="F76" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="H76" s="31" t="s">
+      <c r="H76" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="77" ht="15.0" customHeight="true">
-      <c r="A77" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B77" s="25" t="n">
+      <c r="A77" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="29" t="n">
         <v>13.0</v>
       </c>
-      <c r="C77" s="26" t="s">
+      <c r="C77" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D77" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E77" s="28" t="s">
+      <c r="D77" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="F77" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G77" s="30" t="s">
+      <c r="F77" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H77" s="31" t="s">
+      <c r="H77" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="78" ht="15.0" customHeight="true">
-      <c r="A78" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B78" s="25" t="n">
+      <c r="A78" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" s="29" t="n">
         <v>14.0</v>
       </c>
-      <c r="C78" s="26" t="s">
+      <c r="C78" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D78" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E78" s="28" t="s">
+      <c r="D78" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E78" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="F78" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" s="30" t="s">
+      <c r="F78" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H78" s="31" t="s">
+      <c r="H78" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="79" ht="15.0" customHeight="true">
-      <c r="A79" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B79" s="25" t="n">
+      <c r="A79" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="29" t="n">
         <v>15.0</v>
       </c>
-      <c r="C79" s="26" t="s">
+      <c r="C79" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D79" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E79" s="28" t="s">
+      <c r="D79" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="F79" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G79" s="30" t="s">
+      <c r="F79" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H79" s="31" t="s">
+      <c r="H79" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="80" ht="15.0" customHeight="true">
-      <c r="A80" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B80" s="25" t="n">
+      <c r="A80" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="29" t="n">
         <v>16.0</v>
       </c>
-      <c r="C80" s="26" t="s">
+      <c r="C80" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D80" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E80" s="28" t="s">
+      <c r="D80" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="F80" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G80" s="30" t="s">
+      <c r="F80" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H80" s="31" t="s">
+      <c r="H80" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="81" ht="15.0" customHeight="true">
-      <c r="A81" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B81" s="25" t="n">
+      <c r="A81" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="29" t="n">
         <v>17.0</v>
       </c>
-      <c r="C81" s="26" t="s">
+      <c r="C81" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D81" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E81" s="28" t="s">
+      <c r="D81" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="F81" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G81" s="30" t="s">
+      <c r="F81" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="H81" s="31" t="s">
+      <c r="H81" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="82" ht="15.0" customHeight="true">
-      <c r="A82" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B82" s="25" t="n">
+      <c r="A82" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="29" t="n">
         <v>18.0</v>
       </c>
-      <c r="C82" s="26" t="s">
+      <c r="C82" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D82" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E82" s="28" t="s">
+      <c r="D82" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="F82" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G82" s="30" t="s">
+      <c r="F82" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H82" s="31" t="s">
+      <c r="H82" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="83" ht="15.0" customHeight="true">
-      <c r="A83" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B83" s="25" t="n">
+      <c r="A83" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="29" t="n">
         <v>19.0</v>
       </c>
-      <c r="C83" s="26" t="s">
+      <c r="C83" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D83" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E83" s="28" t="s">
+      <c r="D83" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E83" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="F83" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G83" s="30" t="s">
+      <c r="F83" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H83" s="31" t="s">
+      <c r="H83" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="84" ht="15.0" customHeight="true">
-      <c r="A84" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B84" s="25" t="n">
+      <c r="A84" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="29" t="n">
         <v>20.0</v>
       </c>
-      <c r="C84" s="26" t="s">
+      <c r="C84" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D84" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E84" s="28" t="s">
+      <c r="D84" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E84" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="F84" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G84" s="30" t="s">
+      <c r="F84" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H84" s="31" t="s">
+      <c r="H84" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="85" ht="15.0" customHeight="true">
-      <c r="A85" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B85" s="25" t="n">
+      <c r="A85" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="29" t="n">
         <v>21.0</v>
       </c>
-      <c r="C85" s="26" t="s">
+      <c r="C85" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D85" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E85" s="28" t="s">
+      <c r="D85" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E85" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="F85" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G85" s="30" t="s">
+      <c r="F85" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H85" s="31" t="s">
+      <c r="H85" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="86" ht="15.0" customHeight="true">
-      <c r="A86" s="32"/>
-      <c r="B86" s="33"/>
-      <c r="C86" s="34"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="36"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="38"/>
-      <c r="H86" s="39"/>
+      <c r="A86" s="36"/>
+      <c r="B86" s="37"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="43"/>
     </row>
     <row r="87" ht="15.0" customHeight="true">
-      <c r="A87" s="40" t="s">
+      <c r="A87" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B87" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C87" s="42" t="s">
+      <c r="B87" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C87" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="D87" s="43"/>
-      <c r="E87" s="44"/>
-      <c r="F87" s="45"/>
-      <c r="G87" s="46"/>
-      <c r="H87" s="47"/>
+      <c r="D87" s="47"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="49"/>
+      <c r="G87" s="50"/>
+      <c r="H87" s="51"/>
     </row>
     <row r="88" ht="15.0" customHeight="true">
-      <c r="A88" s="48" t="s">
+      <c r="A88" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B88" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C88" s="50" t="s">
+      <c r="B88" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C88" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="D88" s="51"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="53"/>
-      <c r="G88" s="54"/>
-      <c r="H88" s="55"/>
+      <c r="D88" s="55"/>
+      <c r="E88" s="56"/>
+      <c r="F88" s="57"/>
+      <c r="G88" s="58"/>
+      <c r="H88" s="59"/>
     </row>
     <row r="89" ht="15.0" customHeight="true">
-      <c r="A89" s="56" t="s">
+      <c r="A89" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B89" s="57" t="s">
+      <c r="B89" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C89" s="58" t="s">
+      <c r="C89" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D89" s="59" t="s">
+      <c r="D89" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E89" s="60" t="s">
+      <c r="E89" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F89" s="61" t="s">
+      <c r="F89" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G89" s="62" t="s">
+      <c r="G89" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H89" s="63" t="s">
+      <c r="H89" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="90" ht="15.0" customHeight="true">
-      <c r="A90" s="64" t="s">
+      <c r="A90" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B90" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C90" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D90" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E90" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F90" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="G90" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H90" s="71" t="s">
+      <c r="B90" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C90" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D90" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E90" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F90" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G90" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="91" ht="15.0" customHeight="true">
-      <c r="A91" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="25" t="n">
+      <c r="A91" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="29" t="n">
         <v>1.0</v>
       </c>
-      <c r="C91" s="26" t="s">
+      <c r="C91" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="D91" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E91" s="28" t="s">
+      <c r="D91" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="F91" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G91" s="30" t="s">
+      <c r="F91" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G91" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="H91" s="31" t="s">
+      <c r="H91" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="92" ht="15.0" customHeight="true">
-      <c r="A92" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92" s="25" t="n">
+      <c r="A92" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="29" t="n">
         <v>2.0</v>
       </c>
-      <c r="C92" s="26" t="s">
+      <c r="C92" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D92" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E92" s="28" t="s">
+      <c r="D92" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E92" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F92" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G92" s="30" t="s">
+      <c r="F92" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G92" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H92" s="31" t="s">
+      <c r="H92" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="93" ht="15.0" customHeight="true">
-      <c r="A93" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B93" s="25" t="n">
+      <c r="A93" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="29" t="n">
         <v>3.0</v>
       </c>
-      <c r="C93" s="26" t="s">
+      <c r="C93" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D93" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E93" s="28" t="s">
+      <c r="D93" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E93" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F93" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G93" s="30" t="s">
+      <c r="F93" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H93" s="31" t="s">
+      <c r="H93" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="94" ht="15.0" customHeight="true">
-      <c r="A94" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B94" s="25" t="n">
+      <c r="A94" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="29" t="n">
         <v>4.0</v>
       </c>
-      <c r="C94" s="26" t="s">
+      <c r="C94" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D94" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E94" s="28" t="s">
+      <c r="D94" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E94" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="F94" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G94" s="30" t="s">
+      <c r="F94" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H94" s="31" t="s">
+      <c r="H94" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="95" ht="15.0" customHeight="true">
-      <c r="A95" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="25" t="n">
+      <c r="A95" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="29" t="n">
         <v>5.0</v>
       </c>
-      <c r="C95" s="26" t="s">
+      <c r="C95" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D95" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E95" s="28" t="s">
+      <c r="D95" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E95" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F95" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G95" s="30" t="s">
+      <c r="F95" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H95" s="31" t="s">
+      <c r="H95" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="96" ht="15.0" customHeight="true">
-      <c r="A96" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96" s="25" t="n">
+      <c r="A96" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="29" t="n">
         <v>6.0</v>
       </c>
-      <c r="C96" s="26" t="s">
+      <c r="C96" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="D96" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E96" s="28" t="s">
+      <c r="D96" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E96" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="F96" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G96" s="30" t="s">
+      <c r="F96" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H96" s="31" t="s">
+      <c r="H96" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="97" ht="15.0" customHeight="true">
-      <c r="A97" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B97" s="25" t="n">
+      <c r="A97" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="29" t="n">
         <v>7.0</v>
       </c>
-      <c r="C97" s="26" t="s">
+      <c r="C97" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="D97" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E97" s="28" t="s">
+      <c r="D97" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E97" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="F97" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G97" s="30" t="s">
+      <c r="F97" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H97" s="31" t="s">
+      <c r="H97" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="98" ht="15.0" customHeight="true">
-      <c r="A98" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="25" t="n">
+      <c r="A98" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="29" t="n">
         <v>8.0</v>
       </c>
-      <c r="C98" s="26" t="s">
+      <c r="C98" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D98" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E98" s="28" t="s">
+      <c r="D98" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E98" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="F98" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G98" s="30" t="s">
+      <c r="F98" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G98" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H98" s="31" t="s">
+      <c r="H98" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="99" ht="15.0" customHeight="true">
-      <c r="A99" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" s="25" t="n">
+      <c r="A99" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="29" t="n">
         <v>9.0</v>
       </c>
-      <c r="C99" s="26" t="s">
+      <c r="C99" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="D99" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E99" s="28" t="s">
+      <c r="D99" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E99" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="F99" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G99" s="30" t="s">
+      <c r="F99" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H99" s="31" t="s">
+      <c r="H99" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="100" ht="15.0" customHeight="true">
-      <c r="A100" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B100" s="25" t="n">
+      <c r="A100" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="29" t="n">
         <v>10.0</v>
       </c>
-      <c r="C100" s="26" t="s">
+      <c r="C100" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D100" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E100" s="28" t="s">
+      <c r="D100" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E100" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="F100" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G100" s="30" t="s">
+      <c r="F100" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G100" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H100" s="31" t="s">
+      <c r="H100" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="101" ht="15.0" customHeight="true">
-      <c r="A101" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B101" s="25" t="n">
+      <c r="A101" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B101" s="29" t="n">
         <v>11.0</v>
       </c>
-      <c r="C101" s="26" t="s">
+      <c r="C101" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="D101" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E101" s="28" t="s">
+      <c r="D101" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E101" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="F101" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G101" s="30" t="s">
+      <c r="F101" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H101" s="31" t="s">
+      <c r="H101" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="102" ht="15.0" customHeight="true">
-      <c r="A102" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B102" s="25" t="n">
+      <c r="A102" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B102" s="29" t="n">
         <v>12.0</v>
       </c>
-      <c r="C102" s="26" t="s">
+      <c r="C102" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D102" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E102" s="28" t="s">
+      <c r="D102" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E102" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="F102" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G102" s="30" t="s">
+      <c r="F102" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H102" s="31" t="s">
+      <c r="H102" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="103" ht="15.0" customHeight="true">
-      <c r="A103" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B103" s="25" t="n">
+      <c r="A103" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B103" s="29" t="n">
         <v>13.0</v>
       </c>
-      <c r="C103" s="26" t="s">
+      <c r="C103" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="D103" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E103" s="28" t="s">
+      <c r="D103" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E103" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="F103" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G103" s="30" t="s">
+      <c r="F103" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G103" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H103" s="31" t="s">
+      <c r="H103" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="104" ht="15.0" customHeight="true">
-      <c r="A104" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B104" s="25" t="n">
+      <c r="A104" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" s="29" t="n">
         <v>14.0</v>
       </c>
-      <c r="C104" s="26" t="s">
+      <c r="C104" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="D104" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E104" s="28" t="s">
+      <c r="D104" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E104" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="F104" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G104" s="30" t="s">
+      <c r="F104" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G104" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H104" s="31" t="s">
+      <c r="H104" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="105" ht="15.0" customHeight="true">
-      <c r="A105" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B105" s="25" t="n">
+      <c r="A105" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105" s="29" t="n">
         <v>15.0</v>
       </c>
-      <c r="C105" s="26" t="s">
+      <c r="C105" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="D105" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E105" s="28" t="s">
+      <c r="D105" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E105" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="F105" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G105" s="30" t="s">
+      <c r="F105" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="H105" s="31" t="s">
+      <c r="H105" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="106" ht="15.0" customHeight="true">
-      <c r="A106" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B106" s="25" t="n">
+      <c r="A106" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B106" s="29" t="n">
         <v>16.0</v>
       </c>
-      <c r="C106" s="26" t="s">
+      <c r="C106" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="D106" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E106" s="28" t="s">
+      <c r="D106" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E106" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="F106" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G106" s="30" t="s">
+      <c r="F106" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H106" s="31" t="s">
+      <c r="H106" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="107" ht="15.0" customHeight="true">
-      <c r="A107" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B107" s="25" t="n">
+      <c r="A107" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B107" s="29" t="n">
         <v>17.0</v>
       </c>
-      <c r="C107" s="26" t="s">
+      <c r="C107" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D107" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E107" s="28" t="s">
+      <c r="D107" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E107" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="F107" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G107" s="30" t="s">
+      <c r="F107" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H107" s="31" t="s">
+      <c r="H107" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="108" ht="15.0" customHeight="true">
-      <c r="A108" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B108" s="25" t="n">
+      <c r="A108" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" s="29" t="n">
         <v>18.0</v>
       </c>
-      <c r="C108" s="26" t="s">
+      <c r="C108" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="D108" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E108" s="28" t="s">
+      <c r="D108" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E108" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="F108" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G108" s="30" t="s">
+      <c r="F108" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H108" s="31" t="s">
+      <c r="H108" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="109" ht="15.0" customHeight="true">
-      <c r="A109" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B109" s="25" t="n">
+      <c r="A109" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109" s="29" t="n">
         <v>19.0</v>
       </c>
-      <c r="C109" s="26" t="s">
+      <c r="C109" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="D109" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E109" s="28" t="s">
+      <c r="D109" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E109" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="F109" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G109" s="30" t="s">
+      <c r="F109" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G109" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H109" s="31" t="s">
+      <c r="H109" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="110" ht="15.0" customHeight="true">
-      <c r="A110" s="72" t="s">
+      <c r="A110" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B110" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C110" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D110" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E110" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="F110" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="G110" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="H110" s="79" t="s">
+      <c r="B110" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C110" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E110" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F110" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="H110" s="83" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="111" ht="15.0" customHeight="true">
-      <c r="A111" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B111" s="25" t="n">
+      <c r="A111" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B111" s="29" t="n">
         <v>1.0</v>
       </c>
-      <c r="C111" s="26" t="s">
+      <c r="C111" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="D111" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E111" s="28" t="s">
+      <c r="D111" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E111" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="F111" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G111" s="30" t="s">
+      <c r="F111" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="H111" s="31" t="s">
+      <c r="H111" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="112" ht="15.0" customHeight="true">
-      <c r="A112" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B112" s="25" t="n">
+      <c r="A112" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112" s="29" t="n">
         <v>2.0</v>
       </c>
-      <c r="C112" s="26" t="s">
+      <c r="C112" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="D112" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E112" s="28" t="s">
+      <c r="D112" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E112" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="F112" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G112" s="30" t="s">
+      <c r="F112" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="H112" s="31" t="s">
+      <c r="H112" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="113" ht="15.0" customHeight="true">
-      <c r="A113" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B113" s="25" t="n">
+      <c r="A113" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B113" s="29" t="n">
         <v>3.0</v>
       </c>
-      <c r="C113" s="26" t="s">
+      <c r="C113" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="D113" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E113" s="28" t="s">
+      <c r="D113" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E113" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="F113" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G113" s="30" t="s">
+      <c r="F113" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G113" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H113" s="31" t="s">
+      <c r="H113" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="114" ht="15.0" customHeight="true">
-      <c r="A114" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B114" s="25" t="n">
+      <c r="A114" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" s="29" t="n">
         <v>4.0</v>
       </c>
-      <c r="C114" s="26" t="s">
+      <c r="C114" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="D114" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E114" s="28" t="s">
+      <c r="D114" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E114" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="F114" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G114" s="30" t="s">
+      <c r="F114" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H114" s="31" t="s">
+      <c r="H114" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="115" ht="15.0" customHeight="true">
-      <c r="A115" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B115" s="25" t="n">
+      <c r="A115" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B115" s="29" t="n">
         <v>5.0</v>
       </c>
-      <c r="C115" s="26" t="s">
+      <c r="C115" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="D115" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E115" s="28" t="s">
+      <c r="D115" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E115" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="F115" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G115" s="30" t="s">
+      <c r="F115" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G115" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="H115" s="31" t="s">
+      <c r="H115" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="116" ht="15.0" customHeight="true">
-      <c r="A116" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B116" s="25" t="n">
+      <c r="A116" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B116" s="29" t="n">
         <v>6.0</v>
       </c>
-      <c r="C116" s="26" t="s">
+      <c r="C116" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="D116" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E116" s="28" t="s">
+      <c r="D116" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E116" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="F116" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G116" s="30" t="s">
+      <c r="F116" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G116" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H116" s="31" t="s">
+      <c r="H116" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="117" ht="15.0" customHeight="true">
-      <c r="A117" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B117" s="25" t="n">
+      <c r="A117" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B117" s="29" t="n">
         <v>7.0</v>
       </c>
-      <c r="C117" s="26" t="s">
+      <c r="C117" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="D117" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E117" s="28" t="s">
+      <c r="D117" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E117" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="F117" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G117" s="30" t="s">
+      <c r="F117" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G117" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H117" s="31" t="s">
+      <c r="H117" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="118" ht="15.0" customHeight="true">
-      <c r="A118" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B118" s="25" t="n">
+      <c r="A118" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B118" s="29" t="n">
         <v>8.0</v>
       </c>
-      <c r="C118" s="26" t="s">
+      <c r="C118" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="D118" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E118" s="28" t="s">
+      <c r="D118" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E118" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="F118" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G118" s="30" t="s">
+      <c r="F118" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G118" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H118" s="31" t="s">
+      <c r="H118" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="119" ht="15.0" customHeight="true">
-      <c r="A119" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B119" s="25" t="n">
+      <c r="A119" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" s="29" t="n">
         <v>9.0</v>
       </c>
-      <c r="C119" s="26" t="s">
+      <c r="C119" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="D119" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E119" s="28" t="s">
+      <c r="D119" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E119" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="F119" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G119" s="30" t="s">
+      <c r="F119" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G119" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H119" s="31" t="s">
+      <c r="H119" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="120" ht="15.0" customHeight="true">
-      <c r="A120" s="32"/>
-      <c r="B120" s="33"/>
-      <c r="C120" s="34"/>
-      <c r="D120" s="35"/>
-      <c r="E120" s="36"/>
-      <c r="F120" s="37"/>
-      <c r="G120" s="38"/>
-      <c r="H120" s="39"/>
+      <c r="A120" s="36"/>
+      <c r="B120" s="37"/>
+      <c r="C120" s="38"/>
+      <c r="D120" s="39"/>
+      <c r="E120" s="40"/>
+      <c r="F120" s="41"/>
+      <c r="G120" s="42"/>
+      <c r="H120" s="43"/>
     </row>
     <row r="121" ht="15.0" customHeight="true">
-      <c r="A121" s="40" t="s">
+      <c r="A121" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B121" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C121" s="42" t="s">
+      <c r="B121" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C121" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="D121" s="43"/>
-      <c r="E121" s="44"/>
-      <c r="F121" s="45"/>
-      <c r="G121" s="46"/>
-      <c r="H121" s="47"/>
+      <c r="D121" s="47"/>
+      <c r="E121" s="48"/>
+      <c r="F121" s="49"/>
+      <c r="G121" s="50"/>
+      <c r="H121" s="51"/>
     </row>
     <row r="122" ht="15.0" customHeight="true">
-      <c r="A122" s="48" t="s">
+      <c r="A122" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B122" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C122" s="50" t="s">
+      <c r="B122" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C122" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="D122" s="51"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="53"/>
-      <c r="G122" s="54"/>
-      <c r="H122" s="55"/>
+      <c r="D122" s="55"/>
+      <c r="E122" s="56"/>
+      <c r="F122" s="57"/>
+      <c r="G122" s="58"/>
+      <c r="H122" s="59"/>
     </row>
     <row r="123" ht="15.0" customHeight="true">
-      <c r="A123" s="56" t="s">
+      <c r="A123" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B123" s="57" t="s">
+      <c r="B123" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C123" s="58" t="s">
+      <c r="C123" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D123" s="59" t="s">
+      <c r="D123" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E123" s="60" t="s">
+      <c r="E123" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F123" s="61" t="s">
+      <c r="F123" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G123" s="62" t="s">
+      <c r="G123" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H123" s="63" t="s">
+      <c r="H123" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="124" ht="15.0" customHeight="true">
-      <c r="A124" s="64" t="s">
+      <c r="A124" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B124" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C124" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D124" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E124" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F124" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="G124" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H124" s="71" t="s">
+      <c r="B124" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C124" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E124" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F124" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H124" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="125" ht="15.0" customHeight="true">
-      <c r="A125" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B125" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C125" s="26" t="s">
+      <c r="A125" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D125" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E125" s="28" t="s">
+      <c r="D125" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E125" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="F125" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G125" s="30" t="s">
+      <c r="F125" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H125" s="31" t="s">
+      <c r="H125" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="126" ht="15.0" customHeight="true">
-      <c r="A126" s="32"/>
-      <c r="B126" s="33"/>
-      <c r="C126" s="34"/>
-      <c r="D126" s="35"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="37"/>
-      <c r="G126" s="38"/>
-      <c r="H126" s="39"/>
+      <c r="A126" s="36"/>
+      <c r="B126" s="37"/>
+      <c r="C126" s="38"/>
+      <c r="D126" s="39"/>
+      <c r="E126" s="40"/>
+      <c r="F126" s="41"/>
+      <c r="G126" s="42"/>
+      <c r="H126" s="43"/>
     </row>
     <row r="127" ht="15.0" customHeight="true">
-      <c r="A127" s="40" t="s">
+      <c r="A127" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B127" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C127" s="42" t="s">
+      <c r="B127" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C127" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="D127" s="43"/>
-      <c r="E127" s="44"/>
-      <c r="F127" s="45"/>
-      <c r="G127" s="46"/>
-      <c r="H127" s="47"/>
+      <c r="D127" s="47"/>
+      <c r="E127" s="48"/>
+      <c r="F127" s="49"/>
+      <c r="G127" s="50"/>
+      <c r="H127" s="51"/>
     </row>
     <row r="128" ht="15.0" customHeight="true">
-      <c r="A128" s="48" t="s">
+      <c r="A128" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B128" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C128" s="50" t="s">
+      <c r="B128" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C128" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="D128" s="51"/>
-      <c r="E128" s="52"/>
-      <c r="F128" s="53"/>
-      <c r="G128" s="54"/>
-      <c r="H128" s="55"/>
+      <c r="D128" s="55"/>
+      <c r="E128" s="56"/>
+      <c r="F128" s="57"/>
+      <c r="G128" s="58"/>
+      <c r="H128" s="59"/>
     </row>
     <row r="129" ht="15.0" customHeight="true">
-      <c r="A129" s="56" t="s">
+      <c r="A129" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B129" s="57" t="s">
+      <c r="B129" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C129" s="58" t="s">
+      <c r="C129" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D129" s="59" t="s">
+      <c r="D129" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E129" s="60" t="s">
+      <c r="E129" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F129" s="61" t="s">
+      <c r="F129" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G129" s="62" t="s">
+      <c r="G129" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H129" s="63" t="s">
+      <c r="H129" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="130" ht="15.0" customHeight="true">
-      <c r="A130" s="64" t="s">
+      <c r="A130" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B130" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C130" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D130" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E130" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F130" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="G130" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H130" s="71" t="s">
+      <c r="B130" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C130" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E130" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F130" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G130" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H130" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="131" ht="15.0" customHeight="true">
-      <c r="A131" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B131" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C131" s="26" t="s">
+      <c r="A131" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B131" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C131" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D131" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E131" s="28" t="s">
+      <c r="D131" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E131" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="F131" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G131" s="30" t="s">
+      <c r="F131" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H131" s="31" t="s">
+      <c r="H131" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="132" ht="15.0" customHeight="true">
-      <c r="A132" s="72" t="s">
+      <c r="A132" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B132" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C132" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D132" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E132" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="F132" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="G132" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="H132" s="79" t="s">
+      <c r="B132" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C132" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D132" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E132" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F132" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G132" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="H132" s="83" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="133" ht="15.0" customHeight="true">
-      <c r="A133" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B133" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C133" s="26" t="s">
+      <c r="A133" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B133" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C133" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="D133" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E133" s="28" t="s">
+      <c r="D133" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E133" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="F133" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G133" s="30" t="s">
+      <c r="F133" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G133" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H133" s="31" t="s">
+      <c r="H133" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="134" ht="15.0" customHeight="true">
-      <c r="A134" s="32"/>
-      <c r="B134" s="33"/>
-      <c r="C134" s="34"/>
-      <c r="D134" s="35"/>
-      <c r="E134" s="36"/>
-      <c r="F134" s="37"/>
-      <c r="G134" s="38"/>
-      <c r="H134" s="39"/>
+      <c r="A134" s="36"/>
+      <c r="B134" s="37"/>
+      <c r="C134" s="38"/>
+      <c r="D134" s="39"/>
+      <c r="E134" s="40"/>
+      <c r="F134" s="41"/>
+      <c r="G134" s="42"/>
+      <c r="H134" s="43"/>
     </row>
     <row r="135" ht="15.0" customHeight="true">
-      <c r="A135" s="40" t="s">
+      <c r="A135" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B135" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C135" s="42" t="s">
+      <c r="B135" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C135" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="D135" s="43"/>
-      <c r="E135" s="44"/>
-      <c r="F135" s="45"/>
-      <c r="G135" s="46"/>
-      <c r="H135" s="47"/>
+      <c r="D135" s="47"/>
+      <c r="E135" s="48"/>
+      <c r="F135" s="49"/>
+      <c r="G135" s="50"/>
+      <c r="H135" s="51"/>
     </row>
     <row r="136" ht="15.0" customHeight="true">
-      <c r="A136" s="48" t="s">
+      <c r="A136" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B136" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C136" s="50" t="s">
+      <c r="B136" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C136" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="D136" s="51"/>
-      <c r="E136" s="52"/>
-      <c r="F136" s="53"/>
-      <c r="G136" s="54"/>
-      <c r="H136" s="55"/>
+      <c r="D136" s="55"/>
+      <c r="E136" s="56"/>
+      <c r="F136" s="57"/>
+      <c r="G136" s="58"/>
+      <c r="H136" s="59"/>
     </row>
     <row r="137" ht="15.0" customHeight="true">
-      <c r="A137" s="56" t="s">
+      <c r="A137" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B137" s="57" t="s">
+      <c r="B137" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C137" s="58" t="s">
+      <c r="C137" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D137" s="59" t="s">
+      <c r="D137" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E137" s="60" t="s">
+      <c r="E137" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F137" s="61" t="s">
+      <c r="F137" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G137" s="62" t="s">
+      <c r="G137" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H137" s="63" t="s">
+      <c r="H137" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="138" ht="15.0" customHeight="true">
-      <c r="A138" s="64" t="s">
+      <c r="A138" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B138" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C138" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D138" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E138" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F138" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="G138" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H138" s="71" t="s">
+      <c r="B138" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C138" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D138" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E138" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F138" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G138" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H138" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="139" ht="15.0" customHeight="true">
-      <c r="A139" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B139" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C139" s="26" t="s">
+      <c r="A139" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B139" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C139" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="D139" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E139" s="28" t="s">
+      <c r="D139" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E139" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="F139" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G139" s="30" t="s">
+      <c r="F139" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G139" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H139" s="31" t="s">
+      <c r="H139" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="140" ht="15.0" customHeight="true">
-      <c r="A140" s="72" t="s">
+      <c r="A140" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B140" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C140" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D140" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E140" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="F140" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="G140" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="H140" s="79" t="s">
+      <c r="B140" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C140" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D140" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E140" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F140" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="H140" s="83" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="141" ht="15.0" customHeight="true">
-      <c r="A141" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B141" s="25" t="n">
+      <c r="A141" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B141" s="29" t="n">
         <v>1.0</v>
       </c>
-      <c r="C141" s="26" t="s">
+      <c r="C141" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="D141" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E141" s="28" t="s">
+      <c r="D141" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E141" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F141" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G141" s="30" t="s">
+      <c r="F141" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G141" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="H141" s="31" t="s">
+      <c r="H141" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="142" ht="15.0" customHeight="true">
-      <c r="A142" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B142" s="25" t="n">
+      <c r="A142" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B142" s="29" t="n">
         <v>2.0</v>
       </c>
-      <c r="C142" s="26" t="s">
+      <c r="C142" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D142" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E142" s="28" t="s">
+      <c r="D142" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E142" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="F142" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G142" s="30" t="s">
+      <c r="F142" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G142" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H142" s="31" t="s">
+      <c r="H142" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="143" ht="15.0" customHeight="true">
-      <c r="A143" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B143" s="25" t="n">
+      <c r="A143" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B143" s="29" t="n">
         <v>3.0</v>
       </c>
-      <c r="C143" s="26" t="s">
+      <c r="C143" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D143" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E143" s="28" t="s">
+      <c r="D143" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E143" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F143" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G143" s="30" t="s">
+      <c r="F143" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H143" s="31" t="s">
+      <c r="H143" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="144" ht="15.0" customHeight="true">
-      <c r="A144" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B144" s="25" t="n">
+      <c r="A144" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B144" s="29" t="n">
         <v>4.0</v>
       </c>
-      <c r="C144" s="26" t="s">
+      <c r="C144" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D144" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E144" s="28" t="s">
+      <c r="D144" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E144" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F144" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G144" s="30" t="s">
+      <c r="F144" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H144" s="31" t="s">
+      <c r="H144" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="145" ht="15.0" customHeight="true">
-      <c r="A145" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B145" s="25" t="n">
+      <c r="A145" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B145" s="29" t="n">
         <v>5.0</v>
       </c>
-      <c r="C145" s="26" t="s">
+      <c r="C145" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D145" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E145" s="28" t="s">
+      <c r="D145" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E145" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F145" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G145" s="30" t="s">
+      <c r="F145" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H145" s="31" t="s">
+      <c r="H145" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="146" ht="15.0" customHeight="true">
-      <c r="A146" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B146" s="25" t="n">
+      <c r="A146" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B146" s="29" t="n">
         <v>6.0</v>
       </c>
-      <c r="C146" s="26" t="s">
+      <c r="C146" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D146" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E146" s="28" t="s">
+      <c r="D146" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E146" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F146" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G146" s="30" t="s">
+      <c r="F146" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G146" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H146" s="31" t="s">
+      <c r="H146" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="147" ht="15.0" customHeight="true">
-      <c r="A147" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B147" s="25" t="n">
+      <c r="A147" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B147" s="29" t="n">
         <v>7.0</v>
       </c>
-      <c r="C147" s="26" t="s">
+      <c r="C147" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D147" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E147" s="28" t="s">
+      <c r="D147" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E147" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F147" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G147" s="30" t="s">
+      <c r="F147" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G147" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H147" s="31" t="s">
+      <c r="H147" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="148" ht="15.0" customHeight="true">
-      <c r="A148" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B148" s="25" t="n">
+      <c r="A148" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B148" s="29" t="n">
         <v>8.0</v>
       </c>
-      <c r="C148" s="26" t="s">
+      <c r="C148" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D148" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E148" s="28" t="s">
+      <c r="D148" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E148" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F148" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G148" s="30" t="s">
+      <c r="F148" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G148" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H148" s="31" t="s">
+      <c r="H148" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="149" ht="15.0" customHeight="true">
-      <c r="A149" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B149" s="25" t="n">
+      <c r="A149" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B149" s="29" t="n">
         <v>9.0</v>
       </c>
-      <c r="C149" s="26" t="s">
+      <c r="C149" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D149" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E149" s="28" t="s">
+      <c r="D149" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E149" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F149" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G149" s="30" t="s">
+      <c r="F149" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G149" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H149" s="31" t="s">
+      <c r="H149" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="150" ht="15.0" customHeight="true">
-      <c r="A150" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B150" s="25" t="n">
+      <c r="A150" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B150" s="29" t="n">
         <v>10.0</v>
       </c>
-      <c r="C150" s="26" t="s">
+      <c r="C150" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D150" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E150" s="28" t="s">
+      <c r="D150" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E150" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="F150" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G150" s="30" t="s">
+      <c r="F150" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G150" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H150" s="31" t="s">
+      <c r="H150" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="151" ht="15.0" customHeight="true">
-      <c r="A151" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B151" s="25" t="n">
+      <c r="A151" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B151" s="29" t="n">
         <v>11.0</v>
       </c>
-      <c r="C151" s="26" t="s">
+      <c r="C151" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D151" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E151" s="28" t="s">
+      <c r="D151" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E151" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F151" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G151" s="30" t="s">
+      <c r="F151" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G151" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H151" s="31" t="s">
+      <c r="H151" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="152" ht="15.0" customHeight="true">
-      <c r="A152" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B152" s="25" t="n">
+      <c r="A152" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B152" s="29" t="n">
         <v>12.0</v>
       </c>
-      <c r="C152" s="26" t="s">
+      <c r="C152" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D152" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E152" s="28" t="s">
+      <c r="D152" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E152" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="F152" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G152" s="30" t="s">
+      <c r="F152" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G152" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="H152" s="31" t="s">
+      <c r="H152" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="153" ht="15.0" customHeight="true">
-      <c r="A153" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B153" s="25" t="n">
+      <c r="A153" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B153" s="29" t="n">
         <v>13.0</v>
       </c>
-      <c r="C153" s="26" t="s">
+      <c r="C153" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D153" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E153" s="28" t="s">
+      <c r="D153" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E153" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="F153" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G153" s="30" t="s">
+      <c r="F153" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G153" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H153" s="31" t="s">
+      <c r="H153" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="154" ht="15.0" customHeight="true">
-      <c r="A154" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B154" s="25" t="n">
+      <c r="A154" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B154" s="29" t="n">
         <v>14.0</v>
       </c>
-      <c r="C154" s="26" t="s">
+      <c r="C154" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D154" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E154" s="28" t="s">
+      <c r="D154" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E154" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="F154" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G154" s="30" t="s">
+      <c r="F154" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G154" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H154" s="31" t="s">
+      <c r="H154" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="155" ht="15.0" customHeight="true">
-      <c r="A155" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B155" s="25" t="n">
+      <c r="A155" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B155" s="29" t="n">
         <v>15.0</v>
       </c>
-      <c r="C155" s="26" t="s">
+      <c r="C155" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D155" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E155" s="28" t="s">
+      <c r="D155" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E155" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="F155" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G155" s="30" t="s">
+      <c r="F155" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G155" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H155" s="31" t="s">
+      <c r="H155" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="156" ht="15.0" customHeight="true">
-      <c r="A156" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B156" s="25" t="n">
+      <c r="A156" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B156" s="29" t="n">
         <v>16.0</v>
       </c>
-      <c r="C156" s="26" t="s">
+      <c r="C156" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D156" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E156" s="28" t="s">
+      <c r="D156" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E156" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="F156" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G156" s="30" t="s">
+      <c r="F156" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H156" s="31" t="s">
+      <c r="H156" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="157" ht="15.0" customHeight="true">
-      <c r="A157" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B157" s="25" t="n">
+      <c r="A157" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B157" s="29" t="n">
         <v>17.0</v>
       </c>
-      <c r="C157" s="26" t="s">
+      <c r="C157" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D157" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E157" s="28" t="s">
+      <c r="D157" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E157" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="F157" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G157" s="30" t="s">
+      <c r="F157" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G157" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="H157" s="31" t="s">
+      <c r="H157" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="158" ht="15.0" customHeight="true">
-      <c r="A158" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B158" s="25" t="n">
+      <c r="A158" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B158" s="29" t="n">
         <v>18.0</v>
       </c>
-      <c r="C158" s="26" t="s">
+      <c r="C158" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D158" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E158" s="28" t="s">
+      <c r="D158" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E158" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="F158" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G158" s="30" t="s">
+      <c r="F158" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H158" s="31" t="s">
+      <c r="H158" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="159" ht="15.0" customHeight="true">
-      <c r="A159" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B159" s="25" t="n">
+      <c r="A159" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B159" s="29" t="n">
         <v>19.0</v>
       </c>
-      <c r="C159" s="26" t="s">
+      <c r="C159" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D159" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E159" s="28" t="s">
+      <c r="D159" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E159" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="F159" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G159" s="30" t="s">
+      <c r="F159" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G159" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H159" s="31" t="s">
+      <c r="H159" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="160" ht="15.0" customHeight="true">
-      <c r="A160" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B160" s="25" t="n">
+      <c r="A160" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B160" s="29" t="n">
         <v>20.0</v>
       </c>
-      <c r="C160" s="26" t="s">
+      <c r="C160" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D160" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E160" s="28" t="s">
+      <c r="D160" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E160" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="F160" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G160" s="30" t="s">
+      <c r="F160" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G160" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H160" s="31" t="s">
+      <c r="H160" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="161" ht="15.0" customHeight="true">
-      <c r="A161" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B161" s="25" t="n">
+      <c r="A161" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B161" s="29" t="n">
         <v>21.0</v>
       </c>
-      <c r="C161" s="26" t="s">
+      <c r="C161" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D161" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E161" s="28" t="s">
+      <c r="D161" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E161" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="F161" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G161" s="30" t="s">
+      <c r="F161" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G161" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H161" s="31" t="s">
+      <c r="H161" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="162" ht="15.0" customHeight="true">
-      <c r="A162" s="32"/>
-      <c r="B162" s="33"/>
-      <c r="C162" s="34"/>
-      <c r="D162" s="35"/>
-      <c r="E162" s="36"/>
-      <c r="F162" s="37"/>
-      <c r="G162" s="38"/>
-      <c r="H162" s="39"/>
+      <c r="A162" s="36"/>
+      <c r="B162" s="37"/>
+      <c r="C162" s="38"/>
+      <c r="D162" s="39"/>
+      <c r="E162" s="40"/>
+      <c r="F162" s="41"/>
+      <c r="G162" s="42"/>
+      <c r="H162" s="43"/>
     </row>
     <row r="163" ht="15.0" customHeight="true">
-      <c r="A163" s="40" t="s">
+      <c r="A163" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B163" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C163" s="42" t="s">
+      <c r="B163" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C163" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="D163" s="43"/>
-      <c r="E163" s="44"/>
-      <c r="F163" s="45"/>
-      <c r="G163" s="46"/>
-      <c r="H163" s="47"/>
+      <c r="D163" s="47"/>
+      <c r="E163" s="48"/>
+      <c r="F163" s="49"/>
+      <c r="G163" s="50"/>
+      <c r="H163" s="51"/>
     </row>
     <row r="164" ht="15.0" customHeight="true">
-      <c r="A164" s="48" t="s">
+      <c r="A164" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B164" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C164" s="50" t="s">
+      <c r="B164" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C164" s="54" t="s">
         <v>158</v>
       </c>
-      <c r="D164" s="51"/>
-      <c r="E164" s="52"/>
-      <c r="F164" s="53"/>
-      <c r="G164" s="54"/>
-      <c r="H164" s="55"/>
+      <c r="D164" s="55"/>
+      <c r="E164" s="56"/>
+      <c r="F164" s="57"/>
+      <c r="G164" s="58"/>
+      <c r="H164" s="59"/>
     </row>
     <row r="165" ht="15.0" customHeight="true">
-      <c r="A165" s="56" t="s">
+      <c r="A165" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B165" s="57" t="s">
+      <c r="B165" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C165" s="58" t="s">
+      <c r="C165" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D165" s="59" t="s">
+      <c r="D165" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E165" s="60" t="s">
+      <c r="E165" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F165" s="61" t="s">
+      <c r="F165" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G165" s="62" t="s">
+      <c r="G165" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H165" s="63" t="s">
+      <c r="H165" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="166" ht="15.0" customHeight="true">
-      <c r="A166" s="64" t="s">
+      <c r="A166" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B166" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C166" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D166" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E166" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F166" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="G166" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H166" s="71" t="s">
+      <c r="B166" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C166" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D166" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E166" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F166" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H166" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="167" ht="15.0" customHeight="true">
-      <c r="A167" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B167" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C167" s="26" t="s">
+      <c r="A167" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B167" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C167" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D167" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E167" s="28" t="s">
+      <c r="D167" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E167" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="F167" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G167" s="30" t="s">
+      <c r="F167" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G167" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H167" s="31" t="s">
+      <c r="H167" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="168" ht="15.0" customHeight="true">
-      <c r="A168" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B168" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C168" s="26" t="s">
+      <c r="A168" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B168" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="D168" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E168" s="28" t="s">
+      <c r="D168" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E168" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="F168" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G168" s="30" t="s">
+      <c r="F168" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H168" s="31" t="s">
+      <c r="H168" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="169" ht="15.0" customHeight="true">
-      <c r="A169" s="72" t="s">
+      <c r="A169" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B169" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C169" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D169" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E169" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="F169" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="G169" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="H169" s="79" t="s">
+      <c r="B169" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C169" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D169" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E169" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="H169" s="83" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="170" ht="15.0" customHeight="true">
-      <c r="A170" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B170" s="25" t="n">
+      <c r="A170" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B170" s="29" t="n">
         <v>1.0</v>
       </c>
-      <c r="C170" s="26" t="s">
+      <c r="C170" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="D170" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E170" s="28" t="s">
+      <c r="D170" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E170" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F170" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G170" s="30" t="s">
+      <c r="F170" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="H170" s="31" t="s">
+      <c r="H170" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="171" ht="15.0" customHeight="true">
-      <c r="A171" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B171" s="25" t="n">
+      <c r="A171" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B171" s="29" t="n">
         <v>2.0</v>
       </c>
-      <c r="C171" s="26" t="s">
+      <c r="C171" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D171" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E171" s="28" t="s">
+      <c r="D171" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E171" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="F171" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G171" s="30" t="s">
+      <c r="F171" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H171" s="31" t="s">
+      <c r="H171" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="172" ht="15.0" customHeight="true">
-      <c r="A172" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B172" s="25" t="n">
+      <c r="A172" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B172" s="29" t="n">
         <v>3.0</v>
       </c>
-      <c r="C172" s="26" t="s">
+      <c r="C172" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D172" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E172" s="28" t="s">
+      <c r="D172" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E172" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F172" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G172" s="30" t="s">
+      <c r="F172" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H172" s="31" t="s">
+      <c r="H172" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="173" ht="15.0" customHeight="true">
-      <c r="A173" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B173" s="25" t="n">
+      <c r="A173" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B173" s="29" t="n">
         <v>4.0</v>
       </c>
-      <c r="C173" s="26" t="s">
+      <c r="C173" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D173" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E173" s="28" t="s">
+      <c r="D173" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E173" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F173" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G173" s="30" t="s">
+      <c r="F173" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H173" s="31" t="s">
+      <c r="H173" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="174" ht="15.0" customHeight="true">
-      <c r="A174" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B174" s="25" t="n">
+      <c r="A174" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B174" s="29" t="n">
         <v>5.0</v>
       </c>
-      <c r="C174" s="26" t="s">
+      <c r="C174" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D174" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E174" s="28" t="s">
+      <c r="D174" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E174" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="F174" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G174" s="30" t="s">
+      <c r="F174" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G174" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H174" s="31" t="s">
+      <c r="H174" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="175" ht="15.0" customHeight="true">
-      <c r="A175" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B175" s="25" t="n">
+      <c r="A175" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B175" s="29" t="n">
         <v>6.0</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D175" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E175" s="28" t="s">
+      <c r="D175" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E175" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F175" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G175" s="30" t="s">
+      <c r="F175" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G175" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H175" s="31" t="s">
+      <c r="H175" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="176" ht="15.0" customHeight="true">
-      <c r="A176" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B176" s="25" t="n">
+      <c r="A176" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B176" s="29" t="n">
         <v>7.0</v>
       </c>
-      <c r="C176" s="26" t="s">
+      <c r="C176" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D176" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E176" s="28" t="s">
+      <c r="D176" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E176" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="F176" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G176" s="30" t="s">
+      <c r="F176" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H176" s="31" t="s">
+      <c r="H176" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="177" ht="15.0" customHeight="true">
-      <c r="A177" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B177" s="25" t="n">
+      <c r="A177" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B177" s="29" t="n">
         <v>8.0</v>
       </c>
-      <c r="C177" s="26" t="s">
+      <c r="C177" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D177" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E177" s="28" t="s">
+      <c r="D177" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E177" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F177" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G177" s="30" t="s">
+      <c r="F177" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G177" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H177" s="31" t="s">
+      <c r="H177" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="178" ht="15.0" customHeight="true">
-      <c r="A178" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B178" s="25" t="n">
+      <c r="A178" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B178" s="29" t="n">
         <v>9.0</v>
       </c>
-      <c r="C178" s="26" t="s">
+      <c r="C178" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D178" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E178" s="28" t="s">
+      <c r="D178" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E178" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F178" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G178" s="30" t="s">
+      <c r="F178" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G178" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H178" s="31" t="s">
+      <c r="H178" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="179" ht="15.0" customHeight="true">
-      <c r="A179" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B179" s="25" t="n">
+      <c r="A179" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B179" s="29" t="n">
         <v>10.0</v>
       </c>
-      <c r="C179" s="26" t="s">
+      <c r="C179" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="D179" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E179" s="28" t="s">
+      <c r="D179" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E179" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="F179" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G179" s="30" t="s">
+      <c r="F179" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G179" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="H179" s="31" t="s">
+      <c r="H179" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="180" ht="15.0" customHeight="true">
-      <c r="A180" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B180" s="25" t="n">
+      <c r="A180" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B180" s="29" t="n">
         <v>11.0</v>
       </c>
-      <c r="C180" s="26" t="s">
+      <c r="C180" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D180" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E180" s="28" t="s">
+      <c r="D180" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E180" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F180" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G180" s="30" t="s">
+      <c r="F180" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H180" s="31" t="s">
+      <c r="H180" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="181" ht="15.0" customHeight="true">
-      <c r="A181" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B181" s="25" t="n">
+      <c r="A181" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B181" s="29" t="n">
         <v>12.0</v>
       </c>
-      <c r="C181" s="26" t="s">
+      <c r="C181" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D181" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E181" s="28" t="s">
+      <c r="D181" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E181" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="F181" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G181" s="30" t="s">
+      <c r="F181" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G181" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="H181" s="31" t="s">
+      <c r="H181" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="182" ht="15.0" customHeight="true">
-      <c r="A182" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B182" s="25" t="n">
+      <c r="A182" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B182" s="29" t="n">
         <v>13.0</v>
       </c>
-      <c r="C182" s="26" t="s">
+      <c r="C182" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="D182" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E182" s="28" t="s">
+      <c r="D182" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E182" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="F182" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G182" s="30" t="s">
+      <c r="F182" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G182" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H182" s="31" t="s">
+      <c r="H182" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="183" ht="15.0" customHeight="true">
-      <c r="A183" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B183" s="25" t="n">
+      <c r="A183" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B183" s="29" t="n">
         <v>14.0</v>
       </c>
-      <c r="C183" s="26" t="s">
+      <c r="C183" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="D183" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E183" s="28" t="s">
+      <c r="D183" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E183" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="F183" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G183" s="30" t="s">
+      <c r="F183" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G183" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H183" s="31" t="s">
+      <c r="H183" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="184" ht="15.0" customHeight="true">
-      <c r="A184" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B184" s="25" t="n">
+      <c r="A184" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B184" s="29" t="n">
         <v>15.0</v>
       </c>
-      <c r="C184" s="26" t="s">
+      <c r="C184" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D184" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E184" s="28" t="s">
+      <c r="D184" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E184" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="F184" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G184" s="30" t="s">
+      <c r="F184" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G184" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H184" s="31" t="s">
+      <c r="H184" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="185" ht="15.0" customHeight="true">
-      <c r="A185" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B185" s="25" t="n">
+      <c r="A185" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B185" s="29" t="n">
         <v>16.0</v>
       </c>
-      <c r="C185" s="26" t="s">
+      <c r="C185" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="D185" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E185" s="28" t="s">
+      <c r="D185" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E185" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="F185" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G185" s="30" t="s">
+      <c r="F185" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G185" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H185" s="31" t="s">
+      <c r="H185" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="186" ht="15.0" customHeight="true">
-      <c r="A186" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B186" s="25" t="n">
+      <c r="A186" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B186" s="29" t="n">
         <v>17.0</v>
       </c>
-      <c r="C186" s="26" t="s">
+      <c r="C186" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D186" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E186" s="28" t="s">
+      <c r="D186" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E186" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="F186" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G186" s="30" t="s">
+      <c r="F186" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G186" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="H186" s="31" t="s">
+      <c r="H186" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="187" ht="15.0" customHeight="true">
-      <c r="A187" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B187" s="25" t="n">
+      <c r="A187" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B187" s="29" t="n">
         <v>18.0</v>
       </c>
-      <c r="C187" s="26" t="s">
+      <c r="C187" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D187" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E187" s="28" t="s">
+      <c r="D187" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E187" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="F187" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G187" s="30" t="s">
+      <c r="F187" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G187" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H187" s="31" t="s">
+      <c r="H187" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="188" ht="15.0" customHeight="true">
-      <c r="A188" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B188" s="25" t="n">
+      <c r="A188" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B188" s="29" t="n">
         <v>19.0</v>
       </c>
-      <c r="C188" s="26" t="s">
+      <c r="C188" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D188" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E188" s="28" t="s">
+      <c r="D188" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E188" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="F188" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G188" s="30" t="s">
+      <c r="F188" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G188" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H188" s="31" t="s">
+      <c r="H188" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="189" ht="15.0" customHeight="true">
-      <c r="A189" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B189" s="25" t="n">
+      <c r="A189" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B189" s="29" t="n">
         <v>20.0</v>
       </c>
-      <c r="C189" s="26" t="s">
+      <c r="C189" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D189" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E189" s="28" t="s">
+      <c r="D189" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E189" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="F189" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G189" s="30" t="s">
+      <c r="F189" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G189" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H189" s="31" t="s">
+      <c r="H189" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="190" ht="15.0" customHeight="true">
-      <c r="A190" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B190" s="25" t="n">
+      <c r="A190" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B190" s="29" t="n">
         <v>21.0</v>
       </c>
-      <c r="C190" s="26" t="s">
+      <c r="C190" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="D190" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E190" s="28" t="s">
+      <c r="D190" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E190" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="F190" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G190" s="30" t="s">
+      <c r="F190" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G190" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H190" s="31" t="s">
+      <c r="H190" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="191" ht="15.0" customHeight="true">
-      <c r="A191" s="32"/>
-      <c r="B191" s="33"/>
-      <c r="C191" s="34"/>
-      <c r="D191" s="35"/>
-      <c r="E191" s="36"/>
-      <c r="F191" s="37"/>
-      <c r="G191" s="38"/>
-      <c r="H191" s="39"/>
+      <c r="A191" s="36"/>
+      <c r="B191" s="37"/>
+      <c r="C191" s="38"/>
+      <c r="D191" s="39"/>
+      <c r="E191" s="40"/>
+      <c r="F191" s="41"/>
+      <c r="G191" s="42"/>
+      <c r="H191" s="43"/>
     </row>
     <row r="192" ht="15.0" customHeight="true">
-      <c r="A192" s="40" t="s">
+      <c r="A192" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B192" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C192" s="42" t="s">
+      <c r="B192" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C192" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="D192" s="43"/>
-      <c r="E192" s="44"/>
-      <c r="F192" s="45"/>
-      <c r="G192" s="46"/>
-      <c r="H192" s="47"/>
+      <c r="D192" s="47"/>
+      <c r="E192" s="48"/>
+      <c r="F192" s="49"/>
+      <c r="G192" s="50"/>
+      <c r="H192" s="51"/>
     </row>
     <row r="193" ht="15.0" customHeight="true">
-      <c r="A193" s="48" t="s">
+      <c r="A193" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B193" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C193" s="50" t="s">
+      <c r="B193" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C193" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="D193" s="51"/>
-      <c r="E193" s="52"/>
-      <c r="F193" s="53"/>
-      <c r="G193" s="54"/>
-      <c r="H193" s="55"/>
+      <c r="D193" s="55"/>
+      <c r="E193" s="56"/>
+      <c r="F193" s="57"/>
+      <c r="G193" s="58"/>
+      <c r="H193" s="59"/>
     </row>
     <row r="194" ht="15.0" customHeight="true">
-      <c r="A194" s="56" t="s">
+      <c r="A194" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B194" s="57" t="s">
+      <c r="B194" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C194" s="58" t="s">
+      <c r="C194" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D194" s="59" t="s">
+      <c r="D194" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E194" s="60" t="s">
+      <c r="E194" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F194" s="61" t="s">
+      <c r="F194" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G194" s="62" t="s">
+      <c r="G194" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H194" s="63" t="s">
+      <c r="H194" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="195" ht="15.0" customHeight="true">
-      <c r="A195" s="64" t="s">
+      <c r="A195" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B195" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C195" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D195" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E195" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F195" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="G195" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H195" s="71" t="s">
+      <c r="B195" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C195" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D195" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E195" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F195" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G195" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H195" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="196" ht="15.0" customHeight="true">
-      <c r="A196" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B196" s="25" t="n">
+      <c r="A196" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B196" s="29" t="n">
         <v>1.0</v>
       </c>
-      <c r="C196" s="26" t="s">
+      <c r="C196" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="D196" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E196" s="28" t="s">
+      <c r="D196" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E196" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="F196" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G196" s="30" t="s">
+      <c r="F196" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G196" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="H196" s="31" t="s">
+      <c r="H196" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="197" ht="15.0" customHeight="true">
-      <c r="A197" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B197" s="25" t="n">
+      <c r="A197" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B197" s="29" t="n">
         <v>2.0</v>
       </c>
-      <c r="C197" s="26" t="s">
+      <c r="C197" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="D197" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E197" s="28" t="s">
+      <c r="D197" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E197" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F197" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G197" s="30" t="s">
+      <c r="F197" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G197" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H197" s="31" t="s">
+      <c r="H197" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="198" ht="15.0" customHeight="true">
-      <c r="A198" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B198" s="25" t="n">
+      <c r="A198" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B198" s="29" t="n">
         <v>3.0</v>
       </c>
-      <c r="C198" s="26" t="s">
+      <c r="C198" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D198" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E198" s="28" t="s">
+      <c r="D198" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E198" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F198" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G198" s="30" t="s">
+      <c r="F198" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G198" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H198" s="31" t="s">
+      <c r="H198" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="199" ht="15.0" customHeight="true">
-      <c r="A199" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B199" s="25" t="n">
+      <c r="A199" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B199" s="29" t="n">
         <v>4.0</v>
       </c>
-      <c r="C199" s="26" t="s">
+      <c r="C199" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D199" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E199" s="28" t="s">
+      <c r="D199" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E199" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="F199" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G199" s="30" t="s">
+      <c r="F199" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G199" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H199" s="31" t="s">
+      <c r="H199" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="200" ht="15.0" customHeight="true">
-      <c r="A200" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B200" s="25" t="n">
+      <c r="A200" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B200" s="29" t="n">
         <v>5.0</v>
       </c>
-      <c r="C200" s="26" t="s">
+      <c r="C200" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D200" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E200" s="28" t="s">
+      <c r="D200" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E200" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="F200" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G200" s="30" t="s">
+      <c r="F200" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G200" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H200" s="31" t="s">
+      <c r="H200" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="201" ht="15.0" customHeight="true">
-      <c r="A201" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B201" s="25" t="n">
+      <c r="A201" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B201" s="29" t="n">
         <v>6.0</v>
       </c>
-      <c r="C201" s="26" t="s">
+      <c r="C201" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="D201" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E201" s="28" t="s">
+      <c r="D201" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E201" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="F201" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G201" s="30" t="s">
+      <c r="F201" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G201" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H201" s="31" t="s">
+      <c r="H201" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="202" ht="15.0" customHeight="true">
-      <c r="A202" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B202" s="25" t="n">
+      <c r="A202" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B202" s="29" t="n">
         <v>7.0</v>
       </c>
-      <c r="C202" s="26" t="s">
+      <c r="C202" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="D202" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E202" s="28" t="s">
+      <c r="D202" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E202" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="F202" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G202" s="30" t="s">
+      <c r="F202" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G202" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H202" s="31" t="s">
+      <c r="H202" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="203" ht="15.0" customHeight="true">
-      <c r="A203" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B203" s="25" t="n">
+      <c r="A203" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B203" s="29" t="n">
         <v>8.0</v>
       </c>
-      <c r="C203" s="26" t="s">
+      <c r="C203" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D203" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E203" s="28" t="s">
+      <c r="D203" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E203" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="F203" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G203" s="30" t="s">
+      <c r="F203" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G203" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H203" s="31" t="s">
+      <c r="H203" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="204" ht="15.0" customHeight="true">
-      <c r="A204" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B204" s="25" t="n">
+      <c r="A204" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B204" s="29" t="n">
         <v>9.0</v>
       </c>
-      <c r="C204" s="26" t="s">
+      <c r="C204" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="D204" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E204" s="28" t="s">
+      <c r="D204" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E204" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="F204" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G204" s="30" t="s">
+      <c r="F204" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G204" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H204" s="31" t="s">
+      <c r="H204" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="205" ht="15.0" customHeight="true">
-      <c r="A205" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B205" s="25" t="n">
+      <c r="A205" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B205" s="29" t="n">
         <v>10.0</v>
       </c>
-      <c r="C205" s="26" t="s">
+      <c r="C205" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="D205" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E205" s="28" t="s">
+      <c r="D205" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E205" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="F205" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G205" s="30" t="s">
+      <c r="F205" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G205" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="H205" s="31" t="s">
+      <c r="H205" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="206" ht="15.0" customHeight="true">
-      <c r="A206" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B206" s="25" t="n">
+      <c r="A206" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B206" s="29" t="n">
         <v>11.0</v>
       </c>
-      <c r="C206" s="26" t="s">
+      <c r="C206" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="D206" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E206" s="28" t="s">
+      <c r="D206" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E206" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="F206" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G206" s="30" t="s">
+      <c r="F206" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G206" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H206" s="31" t="s">
+      <c r="H206" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="207" ht="15.0" customHeight="true">
-      <c r="A207" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B207" s="25" t="n">
+      <c r="A207" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B207" s="29" t="n">
         <v>12.0</v>
       </c>
-      <c r="C207" s="26" t="s">
+      <c r="C207" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D207" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E207" s="28" t="s">
+      <c r="D207" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E207" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="F207" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G207" s="30" t="s">
+      <c r="F207" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G207" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H207" s="31" t="s">
+      <c r="H207" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="208" ht="15.0" customHeight="true">
-      <c r="A208" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B208" s="25" t="n">
+      <c r="A208" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B208" s="29" t="n">
         <v>13.0</v>
       </c>
-      <c r="C208" s="26" t="s">
+      <c r="C208" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="D208" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E208" s="28" t="s">
+      <c r="D208" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E208" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="F208" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G208" s="30" t="s">
+      <c r="F208" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G208" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H208" s="31" t="s">
+      <c r="H208" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="209" ht="15.0" customHeight="true">
-      <c r="A209" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B209" s="25" t="n">
+      <c r="A209" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B209" s="29" t="n">
         <v>14.0</v>
       </c>
-      <c r="C209" s="26" t="s">
+      <c r="C209" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="D209" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E209" s="28" t="s">
+      <c r="D209" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E209" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="F209" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G209" s="30" t="s">
+      <c r="F209" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G209" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H209" s="31" t="s">
+      <c r="H209" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="210" ht="15.0" customHeight="true">
-      <c r="A210" s="72" t="s">
+      <c r="A210" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B210" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C210" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D210" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E210" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="F210" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="G210" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="H210" s="79" t="s">
+      <c r="B210" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C210" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D210" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E210" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F210" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G210" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="H210" s="83" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="211" ht="15.0" customHeight="true">
-      <c r="A211" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B211" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C211" s="26" t="s">
+      <c r="A211" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B211" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C211" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="D211" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E211" s="28" t="s">
+      <c r="D211" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E211" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="F211" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G211" s="30" t="s">
+      <c r="F211" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G211" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="H211" s="31" t="s">
+      <c r="H211" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="212" ht="15.0" customHeight="true">
-      <c r="A212" s="32"/>
-      <c r="B212" s="33"/>
-      <c r="C212" s="34"/>
-      <c r="D212" s="35"/>
-      <c r="E212" s="36"/>
-      <c r="F212" s="37"/>
-      <c r="G212" s="38"/>
-      <c r="H212" s="39"/>
+      <c r="A212" s="36"/>
+      <c r="B212" s="37"/>
+      <c r="C212" s="38"/>
+      <c r="D212" s="39"/>
+      <c r="E212" s="40"/>
+      <c r="F212" s="41"/>
+      <c r="G212" s="42"/>
+      <c r="H212" s="43"/>
     </row>
     <row r="213" ht="15.0" customHeight="true">
-      <c r="A213" s="40" t="s">
+      <c r="A213" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="B213" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C213" s="42" t="s">
+      <c r="B213" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C213" s="46" t="s">
         <v>164</v>
       </c>
-      <c r="D213" s="43"/>
-      <c r="E213" s="44"/>
-      <c r="F213" s="45"/>
-      <c r="G213" s="46"/>
-      <c r="H213" s="47"/>
+      <c r="D213" s="47"/>
+      <c r="E213" s="48"/>
+      <c r="F213" s="49"/>
+      <c r="G213" s="50"/>
+      <c r="H213" s="51"/>
     </row>
     <row r="214" ht="15.0" customHeight="true">
-      <c r="A214" s="48" t="s">
+      <c r="A214" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B214" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C214" s="50" t="s">
+      <c r="B214" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C214" s="54" t="s">
         <v>165</v>
       </c>
-      <c r="D214" s="51"/>
-      <c r="E214" s="52"/>
-      <c r="F214" s="53"/>
-      <c r="G214" s="54"/>
-      <c r="H214" s="55"/>
+      <c r="D214" s="55"/>
+      <c r="E214" s="56"/>
+      <c r="F214" s="57"/>
+      <c r="G214" s="58"/>
+      <c r="H214" s="59"/>
     </row>
     <row r="215" ht="15.0" customHeight="true">
-      <c r="A215" s="56" t="s">
+      <c r="A215" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="B215" s="57" t="s">
+      <c r="B215" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="C215" s="58" t="s">
+      <c r="C215" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="D215" s="59" t="s">
+      <c r="D215" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="E215" s="60" t="s">
+      <c r="E215" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F215" s="61" t="s">
+      <c r="F215" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G215" s="62" t="s">
+      <c r="G215" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="H215" s="63" t="s">
+      <c r="H215" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="216" ht="15.0" customHeight="true">
-      <c r="A216" s="64" t="s">
+      <c r="A216" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B216" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C216" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D216" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E216" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="F216" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="G216" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H216" s="71" t="s">
+      <c r="B216" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C216" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="D216" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E216" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F216" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G216" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="H216" s="75" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="217" ht="15.0" customHeight="true">
-      <c r="A217" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B217" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C217" s="26" t="s">
+      <c r="A217" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B217" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C217" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="D217" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E217" s="28" t="s">
+      <c r="D217" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E217" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="F217" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G217" s="30" t="s">
+      <c r="F217" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G217" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="H217" s="31" t="s">
+      <c r="H217" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="218" ht="15.0" customHeight="true">
-      <c r="A218" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B218" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C218" s="26" t="s">
+      <c r="A218" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B218" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C218" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="D218" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E218" s="28" t="s">
+      <c r="D218" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E218" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="F218" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G218" s="30" t="s">
+      <c r="F218" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G218" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H218" s="31" t="s">
+      <c r="H218" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="219" ht="15.0" customHeight="true">
-      <c r="A219" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B219" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C219" s="26" t="s">
+      <c r="A219" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B219" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C219" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="D219" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E219" s="28" t="s">
+      <c r="D219" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E219" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="F219" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G219" s="30" t="s">
+      <c r="F219" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G219" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H219" s="31" t="s">
+      <c r="H219" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="220" ht="15.0" customHeight="true">
-      <c r="A220" s="72" t="s">
+      <c r="A220" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="B220" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C220" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="D220" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E220" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="F220" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="G220" s="78" t="s">
-        <v>22</v>
-      </c>
-      <c r="H220" s="79" t="s">
+      <c r="B220" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C220" s="78" t="s">
+        <v>22</v>
+      </c>
+      <c r="D220" s="79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E220" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="F220" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G220" s="82" t="s">
+        <v>22</v>
+      </c>
+      <c r="H220" s="83" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="221" ht="15.0" customHeight="true">
-      <c r="A221" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B221" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C221" s="26" t="s">
+      <c r="A221" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B221" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C221" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="D221" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E221" s="28" t="s">
+      <c r="D221" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E221" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="F221" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G221" s="30" t="s">
+      <c r="F221" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G221" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H221" s="31" t="s">
+      <c r="H221" s="35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="222" ht="15.0" customHeight="true">
-      <c r="A222" s="32"/>
-      <c r="B222" s="33"/>
-      <c r="C222" s="34"/>
-      <c r="D222" s="35"/>
-      <c r="E222" s="36"/>
-      <c r="F222" s="37"/>
-      <c r="G222" s="38"/>
-      <c r="H222" s="39"/>
+      <c r="A222" s="36"/>
+      <c r="B222" s="37"/>
+      <c r="C222" s="38"/>
+      <c r="D222" s="39"/>
+      <c r="E222" s="40"/>
+      <c r="F222" s="41"/>
+      <c r="G222" s="42"/>
+      <c r="H222" s="43"/>
     </row>
     <row r="223" ht="15.0" customHeight="true">
-      <c r="A223" s="80" t="s">
+      <c r="A223" s="84" t="s">
         <v>170</v>
       </c>
-      <c r="B223" s="81" t="s">
-        <v>22</v>
-      </c>
-      <c r="C223" s="82" t="s">
+      <c r="B223" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C223" s="86" t="s">
         <v>171</v>
       </c>
-      <c r="D223" s="83"/>
-      <c r="E223" s="84"/>
-      <c r="F223" s="85"/>
-      <c r="G223" s="86"/>
-      <c r="H223" s="87"/>
+      <c r="D223" s="87"/>
+      <c r="E223" s="88"/>
+      <c r="F223" s="89"/>
+      <c r="G223" s="90"/>
+      <c r="H223" s="91"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="15">
     <mergeCell ref="A1:B6"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="C2:C3"/>
@@ -6783,7 +6799,13 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A223:B223"/>
+    <mergeCell ref="C223:H223"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/output/OrderRepository.xlsx
+++ b/output/OrderRepository.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="153">
   <si>
     <t>Repository</t>
   </si>
@@ -20,10 +20,16 @@
     <t>Repository概要</t>
   </si>
   <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Method概要</t>
+    <t>SQL_ID</t>
+  </si>
+  <si>
+    <t>SQL概要</t>
+  </si>
+  <si>
+    <t>selectXX</t>
+  </si>
+  <si>
+    <t>XXを取得する</t>
   </si>
   <si>
     <t>区分</t>
@@ -50,6 +56,12 @@
     <t>備考</t>
   </si>
   <si>
+    <t>●INPUT</t>
+  </si>
+  <si>
+    <t>●OUTPUT</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -65,9 +77,6 @@
     <t>IDで注文を取得する。</t>
   </si>
   <si>
-    <t>INPUT</t>
-  </si>
-  <si>
     <t>注文ID</t>
   </si>
   <si>
@@ -75,9 +84,6 @@
   </si>
   <si>
     <t>UUID</t>
-  </si>
-  <si>
-    <t>OUTPUT</t>
   </si>
   <si>
     <t>注文エンティティ。</t>
@@ -834,10 +840,10 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -850,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -872,14 +878,12 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -888,14 +892,12 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -905,652 +907,652 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" t="s" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" t="s" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>21</v>
+      <c r="A16" t="s" s="3">
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>12</v>
+      <c r="A17" t="s" s="3">
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>1.0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="true">
       <c r="A18" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="true">
       <c r="A19" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="true">
       <c r="A20" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="true">
       <c r="A21" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="true">
       <c r="A22" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="true">
       <c r="A23" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="15.0" customHeight="true">
       <c r="A24" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="true">
       <c r="A25" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="true">
       <c r="A26" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" ht="15.0" customHeight="true">
       <c r="A27" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="true">
       <c r="A28" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" ht="15.0" customHeight="true">
       <c r="A29" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" ht="15.0" customHeight="true">
       <c r="A30" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="true">
       <c r="A31" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" ht="15.0" customHeight="true">
       <c r="A32" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" ht="15.0" customHeight="true">
       <c r="A33" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="true">
       <c r="A34" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>18.0</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" ht="15.0" customHeight="true">
       <c r="A35" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>19.0</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="true">
       <c r="A36" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>20.0</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" ht="15.0" customHeight="true">
       <c r="A37" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>21.0</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" ht="15.0" customHeight="true">
@@ -1567,11 +1569,9 @@
       <c r="A39" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B39" s="28"/>
       <c r="C39" s="29" t="s">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="31"/>
@@ -1581,13 +1581,11 @@
     </row>
     <row r="40" ht="15.0" customHeight="true">
       <c r="A40" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="B40" s="36"/>
       <c r="C40" s="37" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D40" s="38"/>
       <c r="E40" s="39"/>
@@ -1597,1172 +1595,1172 @@
     </row>
     <row r="41" ht="15.0" customHeight="true">
       <c r="A41" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B41" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D41" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F41" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G41" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H41" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="true">
       <c r="A42" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B42" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C42" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D42" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E42" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F42" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G42" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H42" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" ht="15.0" customHeight="true">
       <c r="A43" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" ht="15.0" customHeight="true">
       <c r="A44" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="true">
       <c r="A45" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" ht="15.0" customHeight="true">
       <c r="A46" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" ht="15.0" customHeight="true">
       <c r="A47" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="true">
       <c r="A48" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" ht="15.0" customHeight="true">
       <c r="A49" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" ht="15.0" customHeight="true">
       <c r="A50" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B50" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="true">
       <c r="A51" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B51" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" ht="15.0" customHeight="true">
       <c r="A52" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B52" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" ht="15.0" customHeight="true">
       <c r="A53" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B53" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="true">
       <c r="A54" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B54" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" ht="15.0" customHeight="true">
       <c r="A55" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B55" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" ht="15.0" customHeight="true">
       <c r="A56" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B56" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="true">
       <c r="A57" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B57" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" ht="15.0" customHeight="true">
       <c r="A58" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B58" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" ht="15.0" customHeight="true">
       <c r="A59" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B59" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" ht="15.0" customHeight="true">
       <c r="A60" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B60" s="12" t="n">
         <v>18.0</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" ht="15.0" customHeight="true">
       <c r="A61" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B61" s="12" t="n">
         <v>19.0</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" ht="15.0" customHeight="true">
       <c r="A62" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B62" s="12" t="n">
         <v>20.0</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="true">
       <c r="A63" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B63" s="12" t="n">
         <v>21.0</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" ht="15.0" customHeight="true">
       <c r="A64" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B64" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C64" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D64" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E64" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F64" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G64" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H64" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" ht="15.0" customHeight="true">
       <c r="A65" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B65" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="true">
       <c r="A66" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B66" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" ht="15.0" customHeight="true">
       <c r="A67" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B67" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" ht="15.0" customHeight="true">
       <c r="A68" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B68" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="true">
       <c r="A69" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B69" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" ht="15.0" customHeight="true">
       <c r="A70" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B70" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" ht="15.0" customHeight="true">
       <c r="A71" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B71" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="true">
       <c r="A72" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B72" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" ht="15.0" customHeight="true">
       <c r="A73" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B73" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" ht="15.0" customHeight="true">
       <c r="A74" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B74" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" ht="15.0" customHeight="true">
       <c r="A75" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B75" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" ht="15.0" customHeight="true">
       <c r="A76" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B76" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" ht="15.0" customHeight="true">
       <c r="A77" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B77" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H77" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" ht="15.0" customHeight="true">
       <c r="A78" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B78" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" ht="15.0" customHeight="true">
       <c r="A79" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B79" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" ht="15.0" customHeight="true">
       <c r="A80" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B80" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" ht="15.0" customHeight="true">
       <c r="A81" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B81" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" ht="15.0" customHeight="true">
       <c r="A82" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B82" s="12" t="n">
         <v>18.0</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" ht="15.0" customHeight="true">
       <c r="A83" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B83" s="12" t="n">
         <v>19.0</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" ht="15.0" customHeight="true">
       <c r="A84" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B84" s="12" t="n">
         <v>20.0</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" ht="15.0" customHeight="true">
       <c r="A85" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B85" s="12" t="n">
         <v>21.0</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" ht="15.0" customHeight="true">
@@ -2779,11 +2777,9 @@
       <c r="A87" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B87" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B87" s="28"/>
       <c r="C87" s="29" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="D87" s="30"/>
       <c r="E87" s="31"/>
@@ -2793,13 +2789,11 @@
     </row>
     <row r="88" ht="15.0" customHeight="true">
       <c r="A88" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B88" s="36"/>
       <c r="C88" s="37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D88" s="38"/>
       <c r="E88" s="39"/>
@@ -2809,808 +2803,808 @@
     </row>
     <row r="89" ht="15.0" customHeight="true">
       <c r="A89" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B89" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C89" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D89" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E89" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F89" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G89" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H89" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" ht="15.0" customHeight="true">
       <c r="A90" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B90" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C90" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D90" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E90" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F90" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G90" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H90" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" ht="15.0" customHeight="true">
       <c r="A91" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B91" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" ht="15.0" customHeight="true">
       <c r="A92" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B92" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" ht="15.0" customHeight="true">
       <c r="A93" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B93" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G93" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" ht="15.0" customHeight="true">
       <c r="A94" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B94" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C94" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" ht="15.0" customHeight="true">
       <c r="A95" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B95" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C95" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" ht="15.0" customHeight="true">
       <c r="A96" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B96" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C96" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" ht="15.0" customHeight="true">
       <c r="A97" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B97" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C97" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" ht="15.0" customHeight="true">
       <c r="A98" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B98" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" ht="15.0" customHeight="true">
       <c r="A99" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B99" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C99" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" ht="15.0" customHeight="true">
       <c r="A100" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B100" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C100" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H100" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" ht="15.0" customHeight="true">
       <c r="A101" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B101" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C101" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H101" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" ht="15.0" customHeight="true">
       <c r="A102" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B102" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G102" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H102" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" ht="15.0" customHeight="true">
       <c r="A103" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B103" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C103" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G103" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" ht="15.0" customHeight="true">
       <c r="A104" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B104" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C104" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G104" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" ht="15.0" customHeight="true">
       <c r="A105" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B105" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C105" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G105" s="17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" ht="15.0" customHeight="true">
       <c r="A106" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B106" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C106" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F106" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" ht="15.0" customHeight="true">
       <c r="A107" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B107" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C107" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" ht="15.0" customHeight="true">
       <c r="A108" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B108" s="12" t="n">
         <v>18.0</v>
       </c>
       <c r="C108" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F108" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" ht="15.0" customHeight="true">
       <c r="A109" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B109" s="12" t="n">
         <v>19.0</v>
       </c>
       <c r="C109" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F109" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" ht="15.0" customHeight="true">
       <c r="A110" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B110" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C110" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D110" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E110" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F110" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G110" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H110" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" ht="15.0" customHeight="true">
       <c r="A111" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B111" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C111" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H111" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" ht="15.0" customHeight="true">
       <c r="A112" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B112" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C112" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F112" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H112" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" ht="15.0" customHeight="true">
       <c r="A113" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B113" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C113" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F113" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H113" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" ht="15.0" customHeight="true">
       <c r="A114" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B114" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" ht="15.0" customHeight="true">
       <c r="A115" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B115" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F115" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H115" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" ht="15.0" customHeight="true">
       <c r="A116" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B116" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F116" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" ht="15.0" customHeight="true">
       <c r="A117" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B117" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C117" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F117" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H117" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" ht="15.0" customHeight="true">
       <c r="A118" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B118" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C118" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F118" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H118" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" ht="15.0" customHeight="true">
       <c r="A119" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B119" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F119" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H119" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" ht="15.0" customHeight="true">
@@ -3627,11 +3621,9 @@
       <c r="A121" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B121" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B121" s="28"/>
       <c r="C121" s="29" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="D121" s="30"/>
       <c r="E121" s="31"/>
@@ -3641,13 +3633,11 @@
     </row>
     <row r="122" ht="15.0" customHeight="true">
       <c r="A122" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B122" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="B122" s="36"/>
       <c r="C122" s="37" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D122" s="38"/>
       <c r="E122" s="39"/>
@@ -3657,80 +3647,80 @@
     </row>
     <row r="123" ht="15.0" customHeight="true">
       <c r="A123" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B123" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C123" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D123" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E123" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F123" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G123" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H123" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" ht="15.0" customHeight="true">
       <c r="A124" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B124" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C124" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D124" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E124" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F124" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G124" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H124" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" ht="15.0" customHeight="true">
       <c r="A125" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B125" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B125" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H125" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" ht="15.0" customHeight="true">
@@ -3747,11 +3737,9 @@
       <c r="A127" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B127" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B127" s="28"/>
       <c r="C127" s="29" t="s">
-        <v>130</v>
+        <v>3</v>
       </c>
       <c r="D127" s="30"/>
       <c r="E127" s="31"/>
@@ -3761,13 +3749,11 @@
     </row>
     <row r="128" ht="15.0" customHeight="true">
       <c r="A128" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B128" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="B128" s="36"/>
       <c r="C128" s="37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D128" s="38"/>
       <c r="E128" s="39"/>
@@ -3777,132 +3763,132 @@
     </row>
     <row r="129" ht="15.0" customHeight="true">
       <c r="A129" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B129" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C129" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D129" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E129" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F129" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G129" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H129" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130" ht="15.0" customHeight="true">
       <c r="A130" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B130" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C130" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D130" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E130" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F130" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G130" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H130" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" ht="15.0" customHeight="true">
       <c r="A131" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B131" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B131" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H131" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" ht="15.0" customHeight="true">
       <c r="A132" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B132" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C132" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D132" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E132" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F132" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G132" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H132" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" ht="15.0" customHeight="true">
       <c r="A133" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D133" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H133" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" ht="15.0" customHeight="true">
@@ -3919,11 +3905,9 @@
       <c r="A135" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B135" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B135" s="28"/>
       <c r="C135" s="29" t="s">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="D135" s="30"/>
       <c r="E135" s="31"/>
@@ -3933,13 +3917,11 @@
     </row>
     <row r="136" ht="15.0" customHeight="true">
       <c r="A136" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B136" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B136" s="36"/>
       <c r="C136" s="37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D136" s="38"/>
       <c r="E136" s="39"/>
@@ -3949,652 +3931,652 @@
     </row>
     <row r="137" ht="15.0" customHeight="true">
       <c r="A137" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B137" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C137" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D137" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E137" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F137" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G137" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H137" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" ht="15.0" customHeight="true">
       <c r="A138" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B138" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C138" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D138" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E138" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F138" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G138" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H138" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" ht="15.0" customHeight="true">
       <c r="A139" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B139" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B139" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C139" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D139" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F139" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H139" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" ht="15.0" customHeight="true">
       <c r="A140" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B140" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C140" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D140" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E140" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F140" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G140" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H140" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" ht="15.0" customHeight="true">
       <c r="A141" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B141" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C141" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D141" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F141" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G141" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H141" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" ht="15.0" customHeight="true">
       <c r="A142" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B142" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D142" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F142" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G142" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H142" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" ht="15.0" customHeight="true">
       <c r="A143" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B143" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D143" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F143" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H143" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" ht="15.0" customHeight="true">
       <c r="A144" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B144" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D144" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F144" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G144" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H144" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" ht="15.0" customHeight="true">
       <c r="A145" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B145" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D145" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F145" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H145" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146" ht="15.0" customHeight="true">
       <c r="A146" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B146" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C146" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D146" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F146" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H146" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="147" ht="15.0" customHeight="true">
       <c r="A147" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B147" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C147" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D147" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F147" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H147" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="148" ht="15.0" customHeight="true">
       <c r="A148" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B148" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C148" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D148" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F148" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H148" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" ht="15.0" customHeight="true">
       <c r="A149" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B149" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C149" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D149" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F149" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H149" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="150" ht="15.0" customHeight="true">
       <c r="A150" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B150" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C150" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D150" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F150" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H150" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151" ht="15.0" customHeight="true">
       <c r="A151" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B151" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C151" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D151" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F151" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H151" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="152" ht="15.0" customHeight="true">
       <c r="A152" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B152" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C152" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D152" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F152" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" ht="15.0" customHeight="true">
       <c r="A153" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B153" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C153" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D153" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F153" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154" ht="15.0" customHeight="true">
       <c r="A154" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B154" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C154" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D154" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E154" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F154" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H154" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="155" ht="15.0" customHeight="true">
       <c r="A155" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B155" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D155" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F155" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H155" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="156" ht="15.0" customHeight="true">
       <c r="A156" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B156" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C156" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D156" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F156" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G156" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H156" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" ht="15.0" customHeight="true">
       <c r="A157" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B157" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C157" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D157" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F157" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G157" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H157" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" ht="15.0" customHeight="true">
       <c r="A158" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B158" s="12" t="n">
         <v>18.0</v>
       </c>
       <c r="C158" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D158" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F158" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G158" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H158" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" ht="15.0" customHeight="true">
       <c r="A159" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B159" s="12" t="n">
         <v>19.0</v>
       </c>
       <c r="C159" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D159" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F159" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G159" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H159" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="160" ht="15.0" customHeight="true">
       <c r="A160" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B160" s="12" t="n">
         <v>20.0</v>
       </c>
       <c r="C160" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D160" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F160" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H160" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" ht="15.0" customHeight="true">
       <c r="A161" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B161" s="12" t="n">
         <v>21.0</v>
       </c>
       <c r="C161" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D161" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F161" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G161" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H161" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" ht="15.0" customHeight="true">
@@ -4611,11 +4593,9 @@
       <c r="A163" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B163" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B163" s="28"/>
       <c r="C163" s="29" t="s">
-        <v>136</v>
+        <v>3</v>
       </c>
       <c r="D163" s="30"/>
       <c r="E163" s="31"/>
@@ -4625,13 +4605,11 @@
     </row>
     <row r="164" ht="15.0" customHeight="true">
       <c r="A164" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B164" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B164" s="36"/>
       <c r="C164" s="37" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D164" s="38"/>
       <c r="E164" s="39"/>
@@ -4641,678 +4619,678 @@
     </row>
     <row r="165" ht="15.0" customHeight="true">
       <c r="A165" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B165" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C165" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D165" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E165" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F165" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G165" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H165" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="166" ht="15.0" customHeight="true">
       <c r="A166" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B166" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C166" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D166" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E166" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F166" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G166" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H166" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="167" ht="15.0" customHeight="true">
       <c r="A167" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B167" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B167" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C167" s="13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D167" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E167" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F167" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G167" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H167" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="168" ht="15.0" customHeight="true">
       <c r="A168" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B168" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B168" s="12" t="n">
+        <v>2.0</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D168" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F168" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G168" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H168" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169" ht="15.0" customHeight="true">
       <c r="A169" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B169" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C169" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D169" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E169" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F169" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G169" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H169" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="170" ht="15.0" customHeight="true">
       <c r="A170" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B170" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D170" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F170" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G170" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H170" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" ht="15.0" customHeight="true">
       <c r="A171" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B171" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C171" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D171" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E171" s="15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F171" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G171" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H171" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172" ht="15.0" customHeight="true">
       <c r="A172" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B172" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C172" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D172" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E172" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F172" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G172" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H172" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" ht="15.0" customHeight="true">
       <c r="A173" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B173" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C173" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D173" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E173" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F173" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G173" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H173" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" ht="15.0" customHeight="true">
       <c r="A174" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B174" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D174" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F174" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G174" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H174" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" ht="15.0" customHeight="true">
       <c r="A175" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B175" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C175" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D175" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F175" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G175" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H175" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" ht="15.0" customHeight="true">
       <c r="A176" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B176" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C176" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D176" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F176" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H176" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" ht="15.0" customHeight="true">
       <c r="A177" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B177" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C177" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E177" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F177" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G177" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H177" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" ht="15.0" customHeight="true">
       <c r="A178" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B178" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C178" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F178" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G178" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H178" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" ht="15.0" customHeight="true">
       <c r="A179" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B179" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C179" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E179" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F179" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G179" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H179" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="180" ht="15.0" customHeight="true">
       <c r="A180" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B180" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C180" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E180" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F180" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G180" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H180" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181" ht="15.0" customHeight="true">
       <c r="A181" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B181" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C181" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E181" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F181" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G181" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H181" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" ht="15.0" customHeight="true">
       <c r="A182" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B182" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C182" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E182" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F182" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G182" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H182" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" ht="15.0" customHeight="true">
       <c r="A183" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B183" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C183" s="13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E183" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F183" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G183" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H183" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" ht="15.0" customHeight="true">
       <c r="A184" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B184" s="12" t="n">
         <v>15.0</v>
       </c>
       <c r="C184" s="13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D184" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E184" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F184" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G184" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H184" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" ht="15.0" customHeight="true">
       <c r="A185" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B185" s="12" t="n">
         <v>16.0</v>
       </c>
       <c r="C185" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E185" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F185" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G185" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H185" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" ht="15.0" customHeight="true">
       <c r="A186" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B186" s="12" t="n">
         <v>17.0</v>
       </c>
       <c r="C186" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D186" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E186" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F186" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G186" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H186" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" ht="15.0" customHeight="true">
       <c r="A187" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B187" s="12" t="n">
         <v>18.0</v>
       </c>
       <c r="C187" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D187" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E187" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F187" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G187" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H187" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" ht="15.0" customHeight="true">
       <c r="A188" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B188" s="12" t="n">
         <v>19.0</v>
       </c>
       <c r="C188" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D188" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E188" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F188" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G188" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H188" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" ht="15.0" customHeight="true">
       <c r="A189" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B189" s="12" t="n">
         <v>20.0</v>
       </c>
       <c r="C189" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D189" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E189" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F189" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G189" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H189" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" ht="15.0" customHeight="true">
       <c r="A190" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B190" s="12" t="n">
         <v>21.0</v>
       </c>
       <c r="C190" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D190" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E190" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F190" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G190" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H190" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" ht="15.0" customHeight="true">
@@ -5329,11 +5307,9 @@
       <c r="A192" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B192" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B192" s="28"/>
       <c r="C192" s="29" t="s">
-        <v>140</v>
+        <v>3</v>
       </c>
       <c r="D192" s="30"/>
       <c r="E192" s="31"/>
@@ -5343,13 +5319,11 @@
     </row>
     <row r="193" ht="15.0" customHeight="true">
       <c r="A193" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B193" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="B193" s="36"/>
       <c r="C193" s="37" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D193" s="38"/>
       <c r="E193" s="39"/>
@@ -5359,470 +5333,470 @@
     </row>
     <row r="194" ht="15.0" customHeight="true">
       <c r="A194" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B194" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C194" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D194" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E194" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F194" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G194" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H194" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" ht="15.0" customHeight="true">
       <c r="A195" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B195" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C195" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D195" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E195" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F195" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G195" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H195" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="196" ht="15.0" customHeight="true">
       <c r="A196" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B196" s="12" t="n">
         <v>1.0</v>
       </c>
       <c r="C196" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E196" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F196" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G196" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H196" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="197" ht="15.0" customHeight="true">
       <c r="A197" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B197" s="12" t="n">
         <v>2.0</v>
       </c>
       <c r="C197" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D197" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E197" s="15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F197" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G197" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H197" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="198" ht="15.0" customHeight="true">
       <c r="A198" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B198" s="12" t="n">
         <v>3.0</v>
       </c>
       <c r="C198" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E198" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F198" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G198" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H198" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199" ht="15.0" customHeight="true">
       <c r="A199" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B199" s="12" t="n">
         <v>4.0</v>
       </c>
       <c r="C199" s="13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D199" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E199" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F199" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G199" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H199" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="200" ht="15.0" customHeight="true">
       <c r="A200" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B200" s="12" t="n">
         <v>5.0</v>
       </c>
       <c r="C200" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D200" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E200" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F200" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G200" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H200" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="201" ht="15.0" customHeight="true">
       <c r="A201" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B201" s="12" t="n">
         <v>6.0</v>
       </c>
       <c r="C201" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D201" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E201" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F201" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G201" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H201" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="202" ht="15.0" customHeight="true">
       <c r="A202" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B202" s="12" t="n">
         <v>7.0</v>
       </c>
       <c r="C202" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D202" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E202" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F202" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G202" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H202" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203" ht="15.0" customHeight="true">
       <c r="A203" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B203" s="12" t="n">
         <v>8.0</v>
       </c>
       <c r="C203" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D203" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E203" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F203" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G203" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H203" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="204" ht="15.0" customHeight="true">
       <c r="A204" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B204" s="12" t="n">
         <v>9.0</v>
       </c>
       <c r="C204" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D204" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E204" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F204" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G204" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H204" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205" ht="15.0" customHeight="true">
       <c r="A205" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B205" s="12" t="n">
         <v>10.0</v>
       </c>
       <c r="C205" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D205" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E205" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F205" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G205" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H205" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="206" ht="15.0" customHeight="true">
       <c r="A206" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B206" s="12" t="n">
         <v>11.0</v>
       </c>
       <c r="C206" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D206" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E206" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F206" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G206" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H206" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207" ht="15.0" customHeight="true">
       <c r="A207" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B207" s="12" t="n">
         <v>12.0</v>
       </c>
       <c r="C207" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D207" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E207" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F207" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G207" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H207" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208" ht="15.0" customHeight="true">
       <c r="A208" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B208" s="12" t="n">
         <v>13.0</v>
       </c>
       <c r="C208" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D208" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E208" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F208" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G208" s="17" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H208" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209" ht="15.0" customHeight="true">
       <c r="A209" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B209" s="12" t="n">
         <v>14.0</v>
       </c>
       <c r="C209" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E209" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F209" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G209" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H209" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="210" ht="15.0" customHeight="true">
       <c r="A210" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B210" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C210" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D210" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E210" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F210" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G210" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H210" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="211" ht="15.0" customHeight="true">
       <c r="A211" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B211" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C211" s="13" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E211" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F211" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G211" s="17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H211" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="212" ht="15.0" customHeight="true">
@@ -5839,11 +5813,9 @@
       <c r="A213" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B213" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B213" s="28"/>
       <c r="C213" s="29" t="s">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="D213" s="30"/>
       <c r="E213" s="31"/>
@@ -5853,13 +5825,11 @@
     </row>
     <row r="214" ht="15.0" customHeight="true">
       <c r="A214" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B214" s="36" t="s">
-        <v>12</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="B214" s="36"/>
       <c r="C214" s="37" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D214" s="38"/>
       <c r="E214" s="39"/>
@@ -5869,184 +5839,184 @@
     </row>
     <row r="215" ht="15.0" customHeight="true">
       <c r="A215" s="43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B215" s="44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C215" s="45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D215" s="46" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E215" s="47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F215" s="48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G215" s="49" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H215" s="50" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216" ht="15.0" customHeight="true">
       <c r="A216" s="51" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B216" s="52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C216" s="53" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D216" s="54" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E216" s="55" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F216" s="56" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G216" s="57" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H216" s="58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="217" ht="15.0" customHeight="true">
       <c r="A217" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B217" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B217" s="12" t="n">
+        <v>1.0</v>
       </c>
       <c r="C217" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D217" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E217" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F217" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G217" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H217" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="218" ht="15.0" customHeight="true">
       <c r="A218" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B218" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B218" s="12" t="n">
+        <v>2.0</v>
       </c>
       <c r="C218" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D218" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E218" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F218" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G218" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H218" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219" ht="15.0" customHeight="true">
       <c r="A219" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B219" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
+      </c>
+      <c r="B219" s="12" t="n">
+        <v>3.0</v>
       </c>
       <c r="C219" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D219" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E219" s="15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F219" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G219" s="17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H219" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="220" ht="15.0" customHeight="true">
       <c r="A220" s="59" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B220" s="60" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C220" s="61" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D220" s="62" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E220" s="63" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F220" s="64" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G220" s="65" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H220" s="66" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="221" ht="15.0" customHeight="true">
       <c r="A221" s="11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B221" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C221" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D221" s="14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E221" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F221" s="16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G221" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H221" s="18" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="222" ht="15.0" customHeight="true">
@@ -6061,13 +6031,13 @@
     </row>
     <row r="223" ht="15.0" customHeight="true">
       <c r="A223" s="67" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B223" s="68" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C223" s="69" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D223" s="70"/>
       <c r="E223" s="71"/>
@@ -6076,6 +6046,44 @@
       <c r="H223" s="74"/>
     </row>
   </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C87:H87"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C88:H88"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="C121:H121"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="C127:H127"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="C128:H128"/>
+    <mergeCell ref="A135:B135"/>
+    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="A136:B136"/>
+    <mergeCell ref="C136:H136"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="A164:B164"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="A192:B192"/>
+    <mergeCell ref="C192:H192"/>
+    <mergeCell ref="A193:B193"/>
+    <mergeCell ref="C193:H193"/>
+    <mergeCell ref="A213:B213"/>
+    <mergeCell ref="C213:H213"/>
+    <mergeCell ref="A214:B214"/>
+    <mergeCell ref="C214:H214"/>
+  </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/output/OrderRepository.xlsx
+++ b/output/OrderRepository.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1397" uniqueCount="217">
   <si>
     <t xml:space="preserve">Repository</t>
   </si>
@@ -247,9 +247,6 @@
     <t>注文エンティティ。</t>
   </si>
   <si>
-    <t>ORDER</t>
-  </si>
-  <si>
     <t>Order</t>
   </si>
   <si>
@@ -343,7 +340,7 @@
     <t xml:space="preserve">  注文ステータス</t>
   </si>
   <si>
-    <t xml:space="preserve">  STATUS</t>
+    <t xml:space="preserve">  -</t>
   </si>
   <si>
     <t xml:space="preserve">  status</t>
@@ -382,9 +379,6 @@
     <t xml:space="preserve">  注文明細一覧</t>
   </si>
   <si>
-    <t xml:space="preserve">  ITEMS</t>
-  </si>
-  <si>
     <t xml:space="preserve">  items</t>
   </si>
   <si>
@@ -433,9 +427,6 @@
     <t xml:space="preserve">  監査情報</t>
   </si>
   <si>
-    <t xml:space="preserve">  AUDIT_INFO</t>
-  </si>
-  <si>
     <t xml:space="preserve">  auditInfo</t>
   </si>
   <si>
@@ -499,9 +490,6 @@
     <t>検索条件</t>
   </si>
   <si>
-    <t>CONDITION</t>
-  </si>
-  <si>
     <t>condition</t>
   </si>
   <si>
@@ -598,9 +586,6 @@
     <t>ページング要求</t>
   </si>
   <si>
-    <t>PAGE_REQUEST</t>
-  </si>
-  <si>
     <t>pageRequest</t>
   </si>
   <si>
@@ -619,9 +604,6 @@
     <t>ページング結果を表す共通DTO。</t>
   </si>
   <si>
-    <t>PAGE_RESULT</t>
-  </si>
-  <si>
     <t>PageResult</t>
   </si>
   <si>
@@ -631,9 +613,6 @@
     <t xml:space="preserve">  取得結果</t>
   </si>
   <si>
-    <t xml:space="preserve">  CONTENT</t>
-  </si>
-  <si>
     <t xml:space="preserve">  content</t>
   </si>
   <si>
@@ -659,9 +638,6 @@
   </si>
   <si>
     <t xml:space="preserve">  ページング要求</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  PAGE_REQUEST</t>
   </si>
   <si>
     <t xml:space="preserve">  pageRequest</t>
@@ -766,9 +742,6 @@
   </si>
   <si>
     <t>Map</t>
-  </si>
-  <si>
-    <t>MAP</t>
   </si>
   <si>
     <t>Map&lt;String,Object&gt;</t>
@@ -1687,16 +1660,16 @@
         <v>40</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>17</v>
@@ -1710,13 +1683,13 @@
         <v>2.0</v>
       </c>
       <c r="C18" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="E18" s="19" t="s">
         <v>44</v>
-      </c>
-      <c r="E18" s="19" t="s">
-        <v>45</v>
       </c>
       <c r="F18" s="20" t="s">
         <v>37</v>
@@ -1736,19 +1709,19 @@
         <v>3.0</v>
       </c>
       <c r="C19" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="E19" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="F19" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="G19" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H19" s="22" t="s">
         <v>17</v>
@@ -1762,19 +1735,19 @@
         <v>4.0</v>
       </c>
       <c r="C20" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="E20" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="F20" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="G20" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H20" s="22" t="s">
         <v>17</v>
@@ -1788,19 +1761,19 @@
         <v>5.0</v>
       </c>
       <c r="C21" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="E21" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="F21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="H21" s="22" t="s">
         <v>17</v>
@@ -1814,19 +1787,19 @@
         <v>6.0</v>
       </c>
       <c r="C22" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="F22" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="G22" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H22" s="22" t="s">
         <v>17</v>
@@ -1840,19 +1813,19 @@
         <v>7.0</v>
       </c>
       <c r="C23" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="E23" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="F23" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H23" s="22" t="s">
         <v>17</v>
@@ -1866,19 +1839,19 @@
         <v>8.0</v>
       </c>
       <c r="C24" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="E24" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="F24" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H24" s="22" t="s">
         <v>17</v>
@@ -1892,19 +1865,19 @@
         <v>9.0</v>
       </c>
       <c r="C25" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="E25" s="19" t="s">
         <v>73</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>74</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>17</v>
@@ -1918,19 +1891,19 @@
         <v>10.0</v>
       </c>
       <c r="C26" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="E26" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="F26" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>79</v>
       </c>
       <c r="H26" s="22" t="s">
         <v>17</v>
@@ -1944,19 +1917,19 @@
         <v>11.0</v>
       </c>
       <c r="C27" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="E27" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="F27" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="G27" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="H27" s="22" t="s">
         <v>17</v>
@@ -1970,19 +1943,19 @@
         <v>12.0</v>
       </c>
       <c r="C28" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="19" t="s">
         <v>85</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>87</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H28" s="22" t="s">
         <v>17</v>
@@ -1996,19 +1969,19 @@
         <v>13.0</v>
       </c>
       <c r="C29" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F29" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H29" s="22" t="s">
         <v>17</v>
@@ -2022,19 +1995,19 @@
         <v>14.0</v>
       </c>
       <c r="C30" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F30" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H30" s="22" t="s">
         <v>17</v>
@@ -2048,19 +2021,19 @@
         <v>15.0</v>
       </c>
       <c r="C31" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="F31" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="21" t="s">
         <v>96</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G31" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="H31" s="22" t="s">
         <v>17</v>
@@ -2074,19 +2047,19 @@
         <v>16.0</v>
       </c>
       <c r="C32" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>101</v>
-      </c>
       <c r="F32" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H32" s="22" t="s">
         <v>17</v>
@@ -2100,19 +2073,19 @@
         <v>17.0</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H33" s="22" t="s">
         <v>17</v>
@@ -2126,19 +2099,19 @@
         <v>18.0</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F34" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H34" s="22" t="s">
         <v>17</v>
@@ -2152,19 +2125,19 @@
         <v>19.0</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F35" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G35" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H35" s="22" t="s">
         <v>17</v>
@@ -2178,19 +2151,19 @@
         <v>20.0</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F36" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G36" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H36" s="22" t="s">
         <v>17</v>
@@ -2204,19 +2177,19 @@
         <v>21.0</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F37" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H37" s="22" t="s">
         <v>17</v>
@@ -2248,11 +2221,11 @@
     </row>
     <row r="40" ht="15.0" customHeight="true">
       <c r="A40" s="39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B40" s="40"/>
       <c r="C40" s="41" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D40" s="42"/>
       <c r="E40" s="43"/>
@@ -2320,19 +2293,19 @@
         <v>1.0</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F43" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H43" s="22" t="s">
         <v>17</v>
@@ -2346,13 +2319,13 @@
         <v>2.0</v>
       </c>
       <c r="C44" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="E44" s="19" t="s">
         <v>44</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>45</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>37</v>
@@ -2372,19 +2345,19 @@
         <v>3.0</v>
       </c>
       <c r="C45" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="E45" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E45" s="19" t="s">
+      <c r="F45" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="G45" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G45" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H45" s="22" t="s">
         <v>17</v>
@@ -2398,19 +2371,19 @@
         <v>4.0</v>
       </c>
       <c r="C46" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="E46" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="F46" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="G46" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G46" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H46" s="22" t="s">
         <v>17</v>
@@ -2424,19 +2397,19 @@
         <v>5.0</v>
       </c>
       <c r="C47" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="E47" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="F47" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G47" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G47" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="H47" s="22" t="s">
         <v>17</v>
@@ -2450,19 +2423,19 @@
         <v>6.0</v>
       </c>
       <c r="C48" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="E48" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="F48" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="G48" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G48" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H48" s="22" t="s">
         <v>17</v>
@@ -2476,19 +2449,19 @@
         <v>7.0</v>
       </c>
       <c r="C49" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D49" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="E49" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="F49" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G49" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G49" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H49" s="22" t="s">
         <v>17</v>
@@ -2502,19 +2475,19 @@
         <v>8.0</v>
       </c>
       <c r="C50" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="E50" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E50" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="F50" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H50" s="22" t="s">
         <v>17</v>
@@ -2528,19 +2501,19 @@
         <v>9.0</v>
       </c>
       <c r="C51" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D51" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="E51" s="19" t="s">
         <v>73</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>74</v>
       </c>
       <c r="F51" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G51" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H51" s="22" t="s">
         <v>17</v>
@@ -2554,19 +2527,19 @@
         <v>10.0</v>
       </c>
       <c r="C52" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="E52" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E52" s="19" t="s">
+      <c r="F52" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G52" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="F52" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G52" s="21" t="s">
-        <v>79</v>
       </c>
       <c r="H52" s="22" t="s">
         <v>17</v>
@@ -2580,19 +2553,19 @@
         <v>11.0</v>
       </c>
       <c r="C53" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="E53" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="F53" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F53" s="20" t="s">
+      <c r="G53" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="G53" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="H53" s="22" t="s">
         <v>17</v>
@@ -2606,19 +2579,19 @@
         <v>12.0</v>
       </c>
       <c r="C54" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="19" t="s">
         <v>85</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>87</v>
       </c>
       <c r="F54" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H54" s="22" t="s">
         <v>17</v>
@@ -2632,19 +2605,19 @@
         <v>13.0</v>
       </c>
       <c r="C55" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E55" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D55" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F55" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G55" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G55" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H55" s="22" t="s">
         <v>17</v>
@@ -2658,19 +2631,19 @@
         <v>14.0</v>
       </c>
       <c r="C56" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="D56" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F56" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G56" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H56" s="22" t="s">
         <v>17</v>
@@ -2684,19 +2657,19 @@
         <v>15.0</v>
       </c>
       <c r="C57" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="F57" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" s="21" t="s">
         <v>96</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F57" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G57" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="H57" s="22" t="s">
         <v>17</v>
@@ -2710,19 +2683,19 @@
         <v>16.0</v>
       </c>
       <c r="C58" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E58" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D58" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>101</v>
-      </c>
       <c r="F58" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H58" s="22" t="s">
         <v>17</v>
@@ -2736,19 +2709,19 @@
         <v>17.0</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F59" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H59" s="22" t="s">
         <v>17</v>
@@ -2762,19 +2735,19 @@
         <v>18.0</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F60" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G60" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H60" s="22" t="s">
         <v>17</v>
@@ -2788,19 +2761,19 @@
         <v>19.0</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F61" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G61" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G61" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H61" s="22" t="s">
         <v>17</v>
@@ -2814,19 +2787,19 @@
         <v>20.0</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F62" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G62" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H62" s="22" t="s">
         <v>17</v>
@@ -2840,19 +2813,19 @@
         <v>21.0</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F63" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G63" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G63" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H63" s="22" t="s">
         <v>17</v>
@@ -2895,16 +2868,16 @@
         <v>40</v>
       </c>
       <c r="D65" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>42</v>
       </c>
       <c r="F65" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G65" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H65" s="22" t="s">
         <v>17</v>
@@ -2918,13 +2891,13 @@
         <v>2.0</v>
       </c>
       <c r="C66" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="E66" s="19" t="s">
         <v>44</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>45</v>
       </c>
       <c r="F66" s="20" t="s">
         <v>37</v>
@@ -2944,19 +2917,19 @@
         <v>3.0</v>
       </c>
       <c r="C67" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="E67" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E67" s="19" t="s">
+      <c r="F67" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F67" s="20" t="s">
+      <c r="G67" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G67" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H67" s="22" t="s">
         <v>17</v>
@@ -2970,19 +2943,19 @@
         <v>4.0</v>
       </c>
       <c r="C68" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D68" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="E68" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E68" s="19" t="s">
+      <c r="F68" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="G68" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G68" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H68" s="22" t="s">
         <v>17</v>
@@ -2996,19 +2969,19 @@
         <v>5.0</v>
       </c>
       <c r="C69" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="E69" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E69" s="19" t="s">
+      <c r="F69" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G69" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="F69" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G69" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="H69" s="22" t="s">
         <v>17</v>
@@ -3022,19 +2995,19 @@
         <v>6.0</v>
       </c>
       <c r="C70" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="E70" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E70" s="19" t="s">
+      <c r="F70" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F70" s="20" t="s">
+      <c r="G70" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G70" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H70" s="22" t="s">
         <v>17</v>
@@ -3048,19 +3021,19 @@
         <v>7.0</v>
       </c>
       <c r="C71" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D71" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="E71" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E71" s="19" t="s">
+      <c r="F71" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G71" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="F71" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G71" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H71" s="22" t="s">
         <v>17</v>
@@ -3074,19 +3047,19 @@
         <v>8.0</v>
       </c>
       <c r="C72" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D72" s="18" t="s">
+      <c r="E72" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E72" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="F72" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G72" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G72" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H72" s="22" t="s">
         <v>17</v>
@@ -3100,19 +3073,19 @@
         <v>9.0</v>
       </c>
       <c r="C73" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D73" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="E73" s="19" t="s">
         <v>73</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>74</v>
       </c>
       <c r="F73" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G73" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H73" s="22" t="s">
         <v>17</v>
@@ -3126,19 +3099,19 @@
         <v>10.0</v>
       </c>
       <c r="C74" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D74" s="18" t="s">
+      <c r="E74" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="F74" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G74" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G74" s="21" t="s">
-        <v>79</v>
       </c>
       <c r="H74" s="22" t="s">
         <v>17</v>
@@ -3152,19 +3125,19 @@
         <v>11.0</v>
       </c>
       <c r="C75" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D75" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="18" t="s">
+      <c r="E75" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E75" s="19" t="s">
+      <c r="F75" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F75" s="20" t="s">
+      <c r="G75" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="G75" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="H75" s="22" t="s">
         <v>17</v>
@@ -3178,19 +3151,19 @@
         <v>12.0</v>
       </c>
       <c r="C76" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E76" s="19" t="s">
         <v>85</v>
-      </c>
-      <c r="D76" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>87</v>
       </c>
       <c r="F76" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G76" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H76" s="22" t="s">
         <v>17</v>
@@ -3204,19 +3177,19 @@
         <v>13.0</v>
       </c>
       <c r="C77" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E77" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D77" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F77" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G77" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H77" s="22" t="s">
         <v>17</v>
@@ -3230,19 +3203,19 @@
         <v>14.0</v>
       </c>
       <c r="C78" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E78" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="D78" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F78" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G78" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G78" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H78" s="22" t="s">
         <v>17</v>
@@ -3256,19 +3229,19 @@
         <v>15.0</v>
       </c>
       <c r="C79" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E79" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="F79" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G79" s="21" t="s">
         <v>96</v>
-      </c>
-      <c r="E79" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F79" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="H79" s="22" t="s">
         <v>17</v>
@@ -3282,19 +3255,19 @@
         <v>16.0</v>
       </c>
       <c r="C80" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E80" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D80" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>101</v>
-      </c>
       <c r="F80" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G80" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H80" s="22" t="s">
         <v>17</v>
@@ -3308,19 +3281,19 @@
         <v>17.0</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F81" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G81" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H81" s="22" t="s">
         <v>17</v>
@@ -3334,19 +3307,19 @@
         <v>18.0</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F82" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G82" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G82" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H82" s="22" t="s">
         <v>17</v>
@@ -3360,19 +3333,19 @@
         <v>19.0</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F83" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G83" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G83" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H83" s="22" t="s">
         <v>17</v>
@@ -3386,19 +3359,19 @@
         <v>20.0</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F84" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G84" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G84" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H84" s="22" t="s">
         <v>17</v>
@@ -3412,19 +3385,19 @@
         <v>21.0</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F85" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G85" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G85" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H85" s="22" t="s">
         <v>17</v>
@@ -3456,11 +3429,11 @@
     </row>
     <row r="88" ht="15.0" customHeight="true">
       <c r="A88" s="39" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B88" s="40"/>
       <c r="C88" s="41" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D88" s="42"/>
       <c r="E88" s="43"/>
@@ -3528,19 +3501,19 @@
         <v>1.0</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D91" s="18" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F91" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G91" s="21" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H91" s="22" t="s">
         <v>17</v>
@@ -3554,19 +3527,19 @@
         <v>2.0</v>
       </c>
       <c r="C92" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D92" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D92" s="18" t="s">
+      <c r="E92" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E92" s="19" t="s">
+      <c r="F92" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F92" s="20" t="s">
+      <c r="G92" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G92" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H92" s="22" t="s">
         <v>17</v>
@@ -3580,19 +3553,19 @@
         <v>3.0</v>
       </c>
       <c r="C93" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D93" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D93" s="18" t="s">
+      <c r="E93" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E93" s="19" t="s">
+      <c r="F93" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F93" s="20" t="s">
+      <c r="G93" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G93" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H93" s="22" t="s">
         <v>17</v>
@@ -3606,13 +3579,13 @@
         <v>4.0</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D94" s="18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F94" s="20" t="s">
         <v>37</v>
@@ -3632,19 +3605,19 @@
         <v>5.0</v>
       </c>
       <c r="C95" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D95" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D95" s="18" t="s">
+      <c r="E95" s="19" t="s">
         <v>73</v>
-      </c>
-      <c r="E95" s="19" t="s">
-        <v>74</v>
       </c>
       <c r="F95" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G95" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H95" s="22" t="s">
         <v>17</v>
@@ -3658,19 +3631,19 @@
         <v>6.0</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D96" s="18" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F96" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G96" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H96" s="22" t="s">
         <v>17</v>
@@ -3684,19 +3657,19 @@
         <v>7.0</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D97" s="18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G97" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H97" s="22" t="s">
         <v>17</v>
@@ -3710,19 +3683,19 @@
         <v>8.0</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D98" s="18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F98" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G98" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G98" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H98" s="22" t="s">
         <v>17</v>
@@ -3736,19 +3709,19 @@
         <v>9.0</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D99" s="18" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F99" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G99" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G99" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H99" s="22" t="s">
         <v>17</v>
@@ -3762,19 +3735,19 @@
         <v>10.0</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F100" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G100" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H100" s="22" t="s">
         <v>17</v>
@@ -3788,19 +3761,19 @@
         <v>11.0</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F101" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H101" s="22" t="s">
         <v>17</v>
@@ -3814,19 +3787,19 @@
         <v>12.0</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E102" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F102" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G102" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H102" s="22" t="s">
         <v>17</v>
@@ -3840,19 +3813,19 @@
         <v>13.0</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E103" s="19" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F103" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G103" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G103" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H103" s="22" t="s">
         <v>17</v>
@@ -3866,19 +3839,19 @@
         <v>14.0</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D104" s="18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E104" s="19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F104" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G104" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="G104" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="H104" s="22" t="s">
         <v>17</v>
@@ -3892,19 +3865,19 @@
         <v>15.0</v>
       </c>
       <c r="C105" s="17" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="E105" s="19" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F105" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G105" s="21" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H105" s="22" t="s">
         <v>17</v>
@@ -3918,19 +3891,19 @@
         <v>16.0</v>
       </c>
       <c r="C106" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E106" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F106" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G106" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H106" s="22" t="s">
         <v>17</v>
@@ -3944,19 +3917,19 @@
         <v>17.0</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D107" s="18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E107" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G107" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H107" s="22" t="s">
         <v>17</v>
@@ -3970,19 +3943,19 @@
         <v>18.0</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D108" s="18" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E108" s="19" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F108" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G108" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G108" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H108" s="22" t="s">
         <v>17</v>
@@ -3996,19 +3969,19 @@
         <v>19.0</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D109" s="18" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E109" s="19" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F109" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G109" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G109" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H109" s="22" t="s">
         <v>17</v>
@@ -4048,19 +4021,19 @@
         <v>1.0</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D111" s="18" t="s">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="E111" s="19" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F111" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G111" s="21" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H111" s="22" t="s">
         <v>17</v>
@@ -4074,19 +4047,19 @@
         <v>2.0</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D112" s="18" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F112" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G112" s="21" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="H112" s="22" t="s">
         <v>17</v>
@@ -4100,19 +4073,19 @@
         <v>3.0</v>
       </c>
       <c r="C113" s="17" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D113" s="18" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E113" s="19" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F113" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G113" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G113" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H113" s="22" t="s">
         <v>17</v>
@@ -4126,19 +4099,19 @@
         <v>4.0</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D114" s="18" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E114" s="19" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F114" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G114" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H114" s="22" t="s">
         <v>17</v>
@@ -4152,19 +4125,19 @@
         <v>5.0</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="E115" s="19" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F115" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G115" s="21" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H115" s="22" t="s">
         <v>17</v>
@@ -4178,19 +4151,19 @@
         <v>6.0</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D116" s="18" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E116" s="19" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F116" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G116" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H116" s="22" t="s">
         <v>17</v>
@@ -4204,19 +4177,19 @@
         <v>7.0</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D117" s="18" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E117" s="19" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G117" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H117" s="22" t="s">
         <v>17</v>
@@ -4230,19 +4203,19 @@
         <v>8.0</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D118" s="18" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E118" s="19" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F118" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G118" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G118" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H118" s="22" t="s">
         <v>17</v>
@@ -4256,19 +4229,19 @@
         <v>9.0</v>
       </c>
       <c r="C119" s="17" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D119" s="18" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E119" s="19" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F119" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G119" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G119" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H119" s="22" t="s">
         <v>17</v>
@@ -4300,11 +4273,11 @@
     </row>
     <row r="122" ht="15.0" customHeight="true">
       <c r="A122" s="39" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B122" s="40"/>
       <c r="C122" s="41" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D122" s="42"/>
       <c r="E122" s="43"/>
@@ -4375,10 +4348,10 @@
         <v>34</v>
       </c>
       <c r="D125" s="18" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F125" s="20" t="s">
         <v>37</v>
@@ -4436,7 +4409,7 @@
         <v>37</v>
       </c>
       <c r="G127" s="21" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H127" s="22" t="s">
         <v>17</v>
@@ -4468,11 +4441,11 @@
     </row>
     <row r="130" ht="15.0" customHeight="true">
       <c r="A130" s="39" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B130" s="40"/>
       <c r="C130" s="41" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D130" s="42"/>
       <c r="E130" s="43"/>
@@ -4543,10 +4516,10 @@
         <v>34</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E133" s="19" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F133" s="20" t="s">
         <v>37</v>
@@ -4604,7 +4577,7 @@
         <v>37</v>
       </c>
       <c r="G135" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H135" s="22" t="s">
         <v>17</v>
@@ -4636,11 +4609,11 @@
     </row>
     <row r="138" ht="15.0" customHeight="true">
       <c r="A138" s="39" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B138" s="40"/>
       <c r="C138" s="41" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D138" s="42"/>
       <c r="E138" s="43"/>
@@ -4708,19 +4681,19 @@
         <v>1.0</v>
       </c>
       <c r="C141" s="17" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E141" s="19" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F141" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G141" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G141" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H141" s="22" t="s">
         <v>17</v>
@@ -4763,16 +4736,16 @@
         <v>40</v>
       </c>
       <c r="D143" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E143" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="E143" s="19" t="s">
-        <v>42</v>
       </c>
       <c r="F143" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G143" s="21" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="H143" s="22" t="s">
         <v>17</v>
@@ -4786,13 +4759,13 @@
         <v>2.0</v>
       </c>
       <c r="C144" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D144" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D144" s="18" t="s">
+      <c r="E144" s="19" t="s">
         <v>44</v>
-      </c>
-      <c r="E144" s="19" t="s">
-        <v>45</v>
       </c>
       <c r="F144" s="20" t="s">
         <v>37</v>
@@ -4812,19 +4785,19 @@
         <v>3.0</v>
       </c>
       <c r="C145" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D145" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D145" s="18" t="s">
+      <c r="E145" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E145" s="19" t="s">
+      <c r="F145" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F145" s="20" t="s">
+      <c r="G145" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G145" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H145" s="22" t="s">
         <v>17</v>
@@ -4838,19 +4811,19 @@
         <v>4.0</v>
       </c>
       <c r="C146" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D146" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D146" s="18" t="s">
+      <c r="E146" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E146" s="19" t="s">
+      <c r="F146" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F146" s="20" t="s">
+      <c r="G146" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G146" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H146" s="22" t="s">
         <v>17</v>
@@ -4864,19 +4837,19 @@
         <v>5.0</v>
       </c>
       <c r="C147" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D147" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D147" s="18" t="s">
+      <c r="E147" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E147" s="19" t="s">
+      <c r="F147" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G147" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="F147" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G147" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="H147" s="22" t="s">
         <v>17</v>
@@ -4890,19 +4863,19 @@
         <v>6.0</v>
       </c>
       <c r="C148" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D148" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D148" s="18" t="s">
+      <c r="E148" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E148" s="19" t="s">
+      <c r="F148" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F148" s="20" t="s">
+      <c r="G148" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G148" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H148" s="22" t="s">
         <v>17</v>
@@ -4916,19 +4889,19 @@
         <v>7.0</v>
       </c>
       <c r="C149" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D149" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D149" s="18" t="s">
+      <c r="E149" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E149" s="19" t="s">
+      <c r="F149" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G149" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="F149" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G149" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H149" s="22" t="s">
         <v>17</v>
@@ -4942,19 +4915,19 @@
         <v>8.0</v>
       </c>
       <c r="C150" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D150" s="18" t="s">
+      <c r="E150" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E150" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="F150" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G150" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G150" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H150" s="22" t="s">
         <v>17</v>
@@ -4968,19 +4941,19 @@
         <v>9.0</v>
       </c>
       <c r="C151" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D151" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D151" s="18" t="s">
+      <c r="E151" s="19" t="s">
         <v>73</v>
-      </c>
-      <c r="E151" s="19" t="s">
-        <v>74</v>
       </c>
       <c r="F151" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G151" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H151" s="22" t="s">
         <v>17</v>
@@ -4994,19 +4967,19 @@
         <v>10.0</v>
       </c>
       <c r="C152" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D152" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D152" s="18" t="s">
+      <c r="E152" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E152" s="19" t="s">
+      <c r="F152" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G152" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="F152" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G152" s="21" t="s">
-        <v>79</v>
       </c>
       <c r="H152" s="22" t="s">
         <v>17</v>
@@ -5020,19 +4993,19 @@
         <v>11.0</v>
       </c>
       <c r="C153" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D153" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D153" s="18" t="s">
+      <c r="E153" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E153" s="19" t="s">
+      <c r="F153" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F153" s="20" t="s">
+      <c r="G153" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="G153" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="H153" s="22" t="s">
         <v>17</v>
@@ -5046,19 +5019,19 @@
         <v>12.0</v>
       </c>
       <c r="C154" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D154" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E154" s="19" t="s">
         <v>85</v>
-      </c>
-      <c r="D154" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E154" s="19" t="s">
-        <v>87</v>
       </c>
       <c r="F154" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G154" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H154" s="22" t="s">
         <v>17</v>
@@ -5072,19 +5045,19 @@
         <v>13.0</v>
       </c>
       <c r="C155" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D155" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E155" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D155" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E155" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F155" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G155" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G155" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H155" s="22" t="s">
         <v>17</v>
@@ -5098,19 +5071,19 @@
         <v>14.0</v>
       </c>
       <c r="C156" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D156" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E156" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="D156" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E156" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F156" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G156" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G156" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H156" s="22" t="s">
         <v>17</v>
@@ -5124,19 +5097,19 @@
         <v>15.0</v>
       </c>
       <c r="C157" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D157" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E157" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D157" s="18" t="s">
+      <c r="F157" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G157" s="21" t="s">
         <v>96</v>
-      </c>
-      <c r="E157" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F157" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G157" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="H157" s="22" t="s">
         <v>17</v>
@@ -5150,19 +5123,19 @@
         <v>16.0</v>
       </c>
       <c r="C158" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D158" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E158" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D158" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E158" s="19" t="s">
-        <v>101</v>
-      </c>
       <c r="F158" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G158" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H158" s="22" t="s">
         <v>17</v>
@@ -5176,19 +5149,19 @@
         <v>17.0</v>
       </c>
       <c r="C159" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D159" s="18" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E159" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F159" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G159" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H159" s="22" t="s">
         <v>17</v>
@@ -5202,19 +5175,19 @@
         <v>18.0</v>
       </c>
       <c r="C160" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D160" s="18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E160" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F160" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G160" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G160" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H160" s="22" t="s">
         <v>17</v>
@@ -5228,19 +5201,19 @@
         <v>19.0</v>
       </c>
       <c r="C161" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D161" s="18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E161" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F161" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G161" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G161" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H161" s="22" t="s">
         <v>17</v>
@@ -5254,19 +5227,19 @@
         <v>20.0</v>
       </c>
       <c r="C162" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D162" s="18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E162" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F162" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G162" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G162" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H162" s="22" t="s">
         <v>17</v>
@@ -5280,19 +5253,19 @@
         <v>21.0</v>
       </c>
       <c r="C163" s="17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D163" s="18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E163" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F163" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G163" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G163" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H163" s="22" t="s">
         <v>17</v>
@@ -5324,11 +5297,11 @@
     </row>
     <row r="166" ht="15.0" customHeight="true">
       <c r="A166" s="39" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B166" s="40"/>
       <c r="C166" s="41" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D166" s="42"/>
       <c r="E166" s="43"/>
@@ -5399,10 +5372,10 @@
         <v>34</v>
       </c>
       <c r="D169" s="18" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E169" s="19" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F169" s="20" t="s">
         <v>37</v>
@@ -5422,19 +5395,19 @@
         <v>2.0</v>
       </c>
       <c r="C170" s="17" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D170" s="18" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E170" s="19" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F170" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G170" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H170" s="22" t="s">
         <v>17</v>
@@ -5477,16 +5450,16 @@
         <v>40</v>
       </c>
       <c r="D172" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E172" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="E172" s="19" t="s">
-        <v>42</v>
       </c>
       <c r="F172" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G172" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H172" s="22" t="s">
         <v>17</v>
@@ -5500,13 +5473,13 @@
         <v>2.0</v>
       </c>
       <c r="C173" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D173" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D173" s="18" t="s">
+      <c r="E173" s="19" t="s">
         <v>44</v>
-      </c>
-      <c r="E173" s="19" t="s">
-        <v>45</v>
       </c>
       <c r="F173" s="20" t="s">
         <v>37</v>
@@ -5526,19 +5499,19 @@
         <v>3.0</v>
       </c>
       <c r="C174" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D174" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D174" s="18" t="s">
+      <c r="E174" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E174" s="19" t="s">
+      <c r="F174" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F174" s="20" t="s">
+      <c r="G174" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G174" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H174" s="22" t="s">
         <v>17</v>
@@ -5552,19 +5525,19 @@
         <v>4.0</v>
       </c>
       <c r="C175" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D175" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D175" s="18" t="s">
+      <c r="E175" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E175" s="19" t="s">
+      <c r="F175" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F175" s="20" t="s">
+      <c r="G175" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G175" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H175" s="22" t="s">
         <v>17</v>
@@ -5578,19 +5551,19 @@
         <v>5.0</v>
       </c>
       <c r="C176" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D176" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D176" s="18" t="s">
+      <c r="E176" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E176" s="19" t="s">
+      <c r="F176" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G176" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="F176" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G176" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="H176" s="22" t="s">
         <v>17</v>
@@ -5604,19 +5577,19 @@
         <v>6.0</v>
       </c>
       <c r="C177" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D177" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D177" s="18" t="s">
+      <c r="E177" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E177" s="19" t="s">
+      <c r="F177" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F177" s="20" t="s">
+      <c r="G177" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G177" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H177" s="22" t="s">
         <v>17</v>
@@ -5630,19 +5603,19 @@
         <v>7.0</v>
       </c>
       <c r="C178" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D178" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D178" s="18" t="s">
+      <c r="E178" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E178" s="19" t="s">
+      <c r="F178" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G178" s="21" t="s">
         <v>67</v>
-      </c>
-      <c r="F178" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G178" s="21" t="s">
-        <v>68</v>
       </c>
       <c r="H178" s="22" t="s">
         <v>17</v>
@@ -5656,19 +5629,19 @@
         <v>8.0</v>
       </c>
       <c r="C179" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D179" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D179" s="18" t="s">
+      <c r="E179" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E179" s="19" t="s">
-        <v>71</v>
-      </c>
       <c r="F179" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G179" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G179" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H179" s="22" t="s">
         <v>17</v>
@@ -5682,19 +5655,19 @@
         <v>9.0</v>
       </c>
       <c r="C180" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D180" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D180" s="18" t="s">
+      <c r="E180" s="19" t="s">
         <v>73</v>
-      </c>
-      <c r="E180" s="19" t="s">
-        <v>74</v>
       </c>
       <c r="F180" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G180" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H180" s="22" t="s">
         <v>17</v>
@@ -5708,19 +5681,19 @@
         <v>10.0</v>
       </c>
       <c r="C181" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D181" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D181" s="18" t="s">
+      <c r="E181" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E181" s="19" t="s">
+      <c r="F181" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G181" s="21" t="s">
         <v>78</v>
-      </c>
-      <c r="F181" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G181" s="21" t="s">
-        <v>79</v>
       </c>
       <c r="H181" s="22" t="s">
         <v>17</v>
@@ -5734,19 +5707,19 @@
         <v>11.0</v>
       </c>
       <c r="C182" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D182" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D182" s="18" t="s">
+      <c r="E182" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E182" s="19" t="s">
+      <c r="F182" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="F182" s="20" t="s">
+      <c r="G182" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="G182" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="H182" s="22" t="s">
         <v>17</v>
@@ -5760,19 +5733,19 @@
         <v>12.0</v>
       </c>
       <c r="C183" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D183" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E183" s="19" t="s">
         <v>85</v>
-      </c>
-      <c r="D183" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E183" s="19" t="s">
-        <v>87</v>
       </c>
       <c r="F183" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G183" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H183" s="22" t="s">
         <v>17</v>
@@ -5786,19 +5759,19 @@
         <v>13.0</v>
       </c>
       <c r="C184" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D184" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E184" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D184" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E184" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F184" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G184" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G184" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H184" s="22" t="s">
         <v>17</v>
@@ -5812,19 +5785,19 @@
         <v>14.0</v>
       </c>
       <c r="C185" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D185" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="E185" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="D185" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E185" s="19" t="s">
-        <v>94</v>
-      </c>
       <c r="F185" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G185" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G185" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H185" s="22" t="s">
         <v>17</v>
@@ -5838,19 +5811,19 @@
         <v>15.0</v>
       </c>
       <c r="C186" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D186" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E186" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="D186" s="18" t="s">
+      <c r="F186" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G186" s="21" t="s">
         <v>96</v>
-      </c>
-      <c r="E186" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F186" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G186" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="H186" s="22" t="s">
         <v>17</v>
@@ -5864,19 +5837,19 @@
         <v>16.0</v>
       </c>
       <c r="C187" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D187" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E187" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D187" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E187" s="19" t="s">
-        <v>101</v>
-      </c>
       <c r="F187" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G187" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H187" s="22" t="s">
         <v>17</v>
@@ -5890,19 +5863,19 @@
         <v>17.0</v>
       </c>
       <c r="C188" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D188" s="18" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="E188" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F188" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G188" s="21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H188" s="22" t="s">
         <v>17</v>
@@ -5916,19 +5889,19 @@
         <v>18.0</v>
       </c>
       <c r="C189" s="17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D189" s="18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E189" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F189" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G189" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G189" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H189" s="22" t="s">
         <v>17</v>
@@ -5942,19 +5915,19 @@
         <v>19.0</v>
       </c>
       <c r="C190" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D190" s="18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E190" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F190" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G190" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G190" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H190" s="22" t="s">
         <v>17</v>
@@ -5968,19 +5941,19 @@
         <v>20.0</v>
       </c>
       <c r="C191" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D191" s="18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E191" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F191" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G191" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G191" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H191" s="22" t="s">
         <v>17</v>
@@ -5994,19 +5967,19 @@
         <v>21.0</v>
       </c>
       <c r="C192" s="17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D192" s="18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E192" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F192" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G192" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G192" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H192" s="22" t="s">
         <v>17</v>
@@ -6038,11 +6011,11 @@
     </row>
     <row r="195" ht="15.0" customHeight="true">
       <c r="A195" s="39" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B195" s="40"/>
       <c r="C195" s="41" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D195" s="42"/>
       <c r="E195" s="43"/>
@@ -6110,19 +6083,19 @@
         <v>1.0</v>
       </c>
       <c r="C198" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D198" s="18" t="s">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="E198" s="19" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F198" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G198" s="21" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H198" s="22" t="s">
         <v>17</v>
@@ -6136,19 +6109,19 @@
         <v>2.0</v>
       </c>
       <c r="C199" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D199" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D199" s="18" t="s">
+      <c r="E199" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E199" s="19" t="s">
+      <c r="F199" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F199" s="20" t="s">
+      <c r="G199" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G199" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H199" s="22" t="s">
         <v>17</v>
@@ -6162,19 +6135,19 @@
         <v>3.0</v>
       </c>
       <c r="C200" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D200" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D200" s="18" t="s">
+      <c r="E200" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E200" s="19" t="s">
+      <c r="F200" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F200" s="20" t="s">
+      <c r="G200" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G200" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H200" s="22" t="s">
         <v>17</v>
@@ -6188,13 +6161,13 @@
         <v>4.0</v>
       </c>
       <c r="C201" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D201" s="18" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E201" s="19" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F201" s="20" t="s">
         <v>37</v>
@@ -6214,19 +6187,19 @@
         <v>5.0</v>
       </c>
       <c r="C202" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D202" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D202" s="18" t="s">
+      <c r="E202" s="19" t="s">
         <v>73</v>
-      </c>
-      <c r="E202" s="19" t="s">
-        <v>74</v>
       </c>
       <c r="F202" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G202" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H202" s="22" t="s">
         <v>17</v>
@@ -6240,19 +6213,19 @@
         <v>6.0</v>
       </c>
       <c r="C203" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D203" s="18" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E203" s="19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F203" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G203" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H203" s="22" t="s">
         <v>17</v>
@@ -6266,19 +6239,19 @@
         <v>7.0</v>
       </c>
       <c r="C204" s="17" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D204" s="18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E204" s="19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F204" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G204" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H204" s="22" t="s">
         <v>17</v>
@@ -6292,19 +6265,19 @@
         <v>8.0</v>
       </c>
       <c r="C205" s="17" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D205" s="18" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E205" s="19" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F205" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G205" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G205" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H205" s="22" t="s">
         <v>17</v>
@@ -6318,19 +6291,19 @@
         <v>9.0</v>
       </c>
       <c r="C206" s="17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D206" s="18" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E206" s="19" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F206" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G206" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G206" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H206" s="22" t="s">
         <v>17</v>
@@ -6344,19 +6317,19 @@
         <v>10.0</v>
       </c>
       <c r="C207" s="17" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D207" s="18" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E207" s="19" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F207" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G207" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H207" s="22" t="s">
         <v>17</v>
@@ -6370,19 +6343,19 @@
         <v>11.0</v>
       </c>
       <c r="C208" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D208" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E208" s="19" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F208" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G208" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H208" s="22" t="s">
         <v>17</v>
@@ -6396,19 +6369,19 @@
         <v>12.0</v>
       </c>
       <c r="C209" s="17" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D209" s="18" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E209" s="19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F209" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G209" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H209" s="22" t="s">
         <v>17</v>
@@ -6422,19 +6395,19 @@
         <v>13.0</v>
       </c>
       <c r="C210" s="17" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D210" s="18" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E210" s="19" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F210" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G210" s="21" t="s">
         <v>54</v>
-      </c>
-      <c r="G210" s="21" t="s">
-        <v>55</v>
       </c>
       <c r="H210" s="22" t="s">
         <v>17</v>
@@ -6448,19 +6421,19 @@
         <v>14.0</v>
       </c>
       <c r="C211" s="17" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D211" s="18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E211" s="19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F211" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="G211" s="21" t="s">
         <v>83</v>
-      </c>
-      <c r="G211" s="21" t="s">
-        <v>84</v>
       </c>
       <c r="H211" s="22" t="s">
         <v>17</v>
@@ -6500,19 +6473,19 @@
         <v>1.0</v>
       </c>
       <c r="C213" s="17" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D213" s="18" t="s">
-        <v>214</v>
+        <v>37</v>
       </c>
       <c r="E213" s="19" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F213" s="20" t="s">
         <v>37</v>
       </c>
       <c r="G213" s="21" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="H213" s="22" t="s">
         <v>17</v>
@@ -6544,11 +6517,11 @@
     </row>
     <row r="216" ht="15.0" customHeight="true">
       <c r="A216" s="39" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B216" s="40"/>
       <c r="C216" s="41" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D216" s="42"/>
       <c r="E216" s="43"/>
@@ -6616,19 +6589,19 @@
         <v>1.0</v>
       </c>
       <c r="C219" s="17" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D219" s="18" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E219" s="19" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F219" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G219" s="21" t="s">
         <v>49</v>
-      </c>
-      <c r="G219" s="21" t="s">
-        <v>50</v>
       </c>
       <c r="H219" s="22" t="s">
         <v>17</v>
@@ -6642,19 +6615,19 @@
         <v>2.0</v>
       </c>
       <c r="C220" s="17" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D220" s="18" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E220" s="19" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F220" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G220" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G220" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H220" s="22" t="s">
         <v>17</v>
@@ -6668,19 +6641,19 @@
         <v>3.0</v>
       </c>
       <c r="C221" s="17" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D221" s="18" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E221" s="19" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="F221" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G221" s="21" t="s">
         <v>63</v>
-      </c>
-      <c r="G221" s="21" t="s">
-        <v>64</v>
       </c>
       <c r="H221" s="22" t="s">
         <v>17</v>
@@ -6732,7 +6705,7 @@
         <v>37</v>
       </c>
       <c r="G223" s="21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H223" s="22" t="s">
         <v>17</v>
@@ -6750,13 +6723,13 @@
     </row>
     <row r="225" ht="15.0" customHeight="true">
       <c r="A225" s="71" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B225" s="72" t="s">
         <v>17</v>
       </c>
       <c r="C225" s="73" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D225" s="74"/>
       <c r="E225" s="75"/>
